--- a/excel_name_change/excel_files/GPO-001 - Goods Purchase - CIF Catalog - Low Dollar.xlsx
+++ b/excel_name_change/excel_files/GPO-001 - Goods Purchase - CIF Catalog - Low Dollar.xlsx
@@ -1,167 +1,566 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samit paudel\Downloads\ariba_automation\sap_test_automation\excel_name_change\excel_files\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="878" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="-120" windowWidth="23040" windowHeight="9192" tabRatio="878" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenario Cover Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Steps" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="References" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Scenario Cover Sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Steps" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="References" sheetId="4" r:id="rId4"/>
     <sheet name="Scenario Metrics " sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="12404" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="125">
+  <si>
+    <t xml:space="preserve">__changed Owner: </t>
+  </si>
+  <si>
+    <t>Test Cycle:</t>
+  </si>
+  <si>
+    <t>__changed ID:</t>
+  </si>
+  <si>
+    <t>GPO-001</t>
+  </si>
+  <si>
+    <t>Test Objective:</t>
+  </si>
+  <si>
+    <t>Create PR and PO in guided buying.</t>
+  </si>
+  <si>
+    <t>__changed Description:</t>
+  </si>
+  <si>
+    <t>Long Description __changed Summary for items to be tested</t>
+  </si>
+  <si>
+    <t>Search catalog for items
+Add items to cart
+Complete requisition details and submit
+Review PR approval flow 
+Confirm PO generation
+Create associated receipt</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Data Requirements</t>
+  </si>
+  <si>
+    <t>Legacy Reference</t>
+  </si>
+  <si>
+    <t>SAP Reference</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prerequisite </t>
+  </si>
+  <si>
+    <t>Key RICEF Objects</t>
+  </si>
+  <si>
+    <t>Master Data Validation</t>
+  </si>
+  <si>
+    <t>SAP PO Post and Validation</t>
+  </si>
+  <si>
+    <t>SAP Invoice to SAP</t>
+  </si>
+  <si>
+    <t>Payment Remitance Validation to Ariba</t>
+  </si>
+  <si>
+    <t>TEST SRIPT &amp; EXECUTION APPROVAL</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Signature</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>__changed Number</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description </t>
+  </si>
+  <si>
+    <t>Tcode</t>
+  </si>
+  <si>
+    <t>Test Data / Test Execution</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Step Completed
+Sucessfullyåç</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>FI Impact</t>
+  </si>
+  <si>
+    <t>RICEF Tested</t>
+  </si>
+  <si>
+    <t>TPR #</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Tester/User ID</t>
+  </si>
+  <si>
+    <t>Y or N</t>
+  </si>
+  <si>
+    <t>__changed No.</t>
+  </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>BL_001</t>
+  </si>
+  <si>
+    <t>env</t>
+  </si>
+  <si>
+    <t>Buyer</t>
+  </si>
+  <si>
+    <t>Complete script GEN-001 to log into Guided Buying.</t>
+  </si>
+  <si>
+    <t>Login
+Password</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nexus Water Group homepage is presented. </t>
+  </si>
+  <si>
+    <t>Catalog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_enter_ search term In the box containing the message "Find goods and services", search for a catalog item by name.
+Click on Magnifying glass after entering the item name on box. </t>
+  </si>
+  <si>
+    <t>"goggles"</t>
+  </si>
+  <si>
+    <t>Search results from the  company catalog are  displayed.</t>
+  </si>
+  <si>
+    <t>Hover on the desired item.</t>
+  </si>
+  <si>
+    <t>Use the +/- buttons to increase or decrease the quantity.</t>
+  </si>
+  <si>
+    <t>Safety Goggles - Pro-Safe - Direct Ventilation
+$3.49 USD / each</t>
+  </si>
+  <si>
+    <t>Quantity can be increased or decreased as desired.</t>
+  </si>
+  <si>
+    <t>_enter_ the desired quantity  in the "Qty" box.</t>
+  </si>
+  <si>
+    <t>Quantity: 30</t>
+  </si>
+  <si>
+    <t>Desired quantity is indicated.</t>
+  </si>
+  <si>
+    <t>Press "Add to Cart" button.</t>
+  </si>
+  <si>
+    <t>Shopping Cart popup  window appears.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review the details on the shopping pop-up cart displayed at top right of screen.
+</t>
+  </si>
+  <si>
+    <t>Details are reviewed.</t>
+  </si>
+  <si>
+    <t>Checkout items in the cart by pressing "Check Out".
+Record the PR reference number as a result in Column K - Actual Result.</t>
+  </si>
+  <si>
+    <t>Requisition screen appears. The system assigns the PR number to the document.</t>
+  </si>
+  <si>
+    <t>Requisition Header</t>
+  </si>
+  <si>
+    <t>_enter_ the requistion title on "Requistion title" box.</t>
+  </si>
+  <si>
+    <t>Safety Goggles Test PR</t>
+  </si>
+  <si>
+    <t>Requisition title is updated.</t>
+  </si>
+  <si>
+    <t>_enter_ or verify the remaining data elements on the Requistion screen.
+Note: Only "red " items should be editable.</t>
+  </si>
+  <si>
+    <t>Need-by Date: Today + 7 days
+Deliver To: [Your Name ]
+Purchasing Unit:	[Leave default]
+On Behalf Of: [Your Name ]
+Plant: [Leave default]
+Company Code: [Leave default]</t>
+  </si>
+  <si>
+    <t>Fields are updated without any error.</t>
+  </si>
+  <si>
+    <t>Requisition Lines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_enter_ or  verify the information under the header area of item 1: 
+(Click on &gt; button on left of item image to expand the section )                             Note: Only "red " items should be editable.
+</t>
+  </si>
+  <si>
+    <t>Safety Goggles - Pro-Safe - Direct Ventilation
+Quantity : 1
+Net Amount: $3.49 USD
+Gross Amount: $3.49 USD
+Contact : Ariba Network Account</t>
+  </si>
+  <si>
+    <t>Fields are updated</t>
+  </si>
+  <si>
+    <t>Click on &gt; button on left of "Accounting" to expand the section.
+_enter_ or  verify the information in the Accounting  section. 
+Note: only red items should be editable.</t>
+  </si>
+  <si>
+    <t>Account Type: K (Cost Center)
+Item Category : Standard
+Bill To: 3020 (Texas Water Utilities, L.P.)
+Account Assignment : K (Cost center)
+GL Account:  Use default
+Cost Center: Use default</t>
+  </si>
+  <si>
+    <t>Click on &gt; button on left of "Shipping" to expand the section.
+_enter_ or  verify the information in the Shipping  section. 
+Note: only red items should be editable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery Address: Use default
+Deliver To: [Your Name ]
+Need-by Date: Today +7
+Purchase Group: Use default
+</t>
+  </si>
+  <si>
+    <t>Click on &gt; button on left of "Others" to expand this section.
+_enter_ or  verify the information in the Others section. 
+Note: only red items should be editable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commodity Code : 441115 (Organizers and accessories)
+Material Group : YBZ02 (Product Group Supplies)
+Item Category : Material
+Payment Terms :  Use default
+SAPPlant :  Use default
+Purch Org :  Use default
+Line item Text : [IGNORE]
+</t>
+  </si>
+  <si>
+    <t>Fields are updated.</t>
+  </si>
+  <si>
+    <t>Requisition Header Comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access the comments section. 
+_enter_ the information in the "Write your Comments"  section.                            
+Using the chooser, determine or verify if the comment should be visible to the supplier. 
+Note : only red items should be editable. </t>
+  </si>
+  <si>
+    <t>Comments: [Blank]
+Share with Supplier: [Not Checked]</t>
+  </si>
+  <si>
+    <t>You are able to write the comments with the desired visibility of the supplier.</t>
+  </si>
+  <si>
+    <t>Press "Add"  to save Comments updates.</t>
+  </si>
+  <si>
+    <t>Added Comments page is displayed. Comments section displays Creator, Comment, Shared with supplier info and date created.</t>
+  </si>
+  <si>
+    <t>Requisition Header Attachments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access "Attachments" section. 
+Press "Browse" to add an attachment.
+</t>
+  </si>
+  <si>
+    <t>File system window appears</t>
+  </si>
+  <si>
+    <t>Select the desired file to be attached, and press "Open".</t>
+  </si>
+  <si>
+    <t>File is uploaded to Ariba Buying. File name is displayed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using the checkbox , determine or verify if the attachement should be visible to the supplier. </t>
+  </si>
+  <si>
+    <t>Share with Supplier: [Not selected]</t>
+  </si>
+  <si>
+    <t>Press "Add"  to save Attachment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Attachment file name, size, Creator, and visible to supplier on Order is visible.</t>
+  </si>
+  <si>
+    <t>Approval Flow</t>
+  </si>
+  <si>
+    <t>Verify the approval flow displayed under Approval Flow header at bottom of the screen.</t>
+  </si>
+  <si>
+    <t>Approver/s are shown.</t>
+  </si>
+  <si>
+    <t>Respective approvers are displayed.</t>
+  </si>
+  <si>
+    <t>Requisition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Press "Submit"  to submit the requisition for approval. </t>
+  </si>
+  <si>
+    <t>Message appears "Your requisition has been sent for approval.</t>
+  </si>
+  <si>
+    <t>View Approval Flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click on View Requisition to display the created requisiton. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Submitted</t>
+  </si>
+  <si>
+    <t>The PR is now on Submitted status.
+Approval Flow is now active shown by green flow.</t>
+  </si>
+  <si>
+    <t>Count of Status</t>
+  </si>
+  <si>
+    <t>(blank)</t>
+  </si>
+  <si>
+    <t>10 - Not Started</t>
+  </si>
+  <si>
+    <t>20 - In-Process</t>
+  </si>
+  <si>
+    <t>30 - TPR Hold</t>
+  </si>
+  <si>
+    <t>40 - DEV Hold</t>
+  </si>
+  <si>
+    <t>50 - Pass</t>
+  </si>
+  <si>
+    <t>60 - N/A</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>PP_018</t>
+  </si>
+  <si>
+    <t>RTR</t>
+  </si>
+  <si>
+    <t>PTP</t>
+  </si>
+  <si>
+    <t>PP</t>
+  </si>
+  <si>
+    <t>IMWM</t>
+  </si>
+  <si>
+    <t>PP_018 Total</t>
+  </si>
+  <si>
+    <t>ZZZ999</t>
+  </si>
+  <si>
+    <t>ZZZ999 Total</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
-      <sz val="9"/>
     </font>
     <font>
+      <b/>
+      <i/>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <i val="1"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="9"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <sz val="8"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
-      <sz val="10"/>
     </font>
     <font>
+      <i/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <sz val="12"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
+      <sz val="14"/>
       <name val="Calibri"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <color rgb="FF000000"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
-      <color rgb="FF0070C0"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
       <name val="Calibri"/>
-      <color rgb="FF00B050"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="14"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <color rgb="FFFF0000"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF262626"/>
       <name val="Calibri"/>
-      <color theme="1"/>
-      <sz val="14"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="FF00B0F0"/>
-      <sz val="14"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="FF262626"/>
-      <sz val="14"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF0070C0"/>
-      <sz val="14"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF0070C0"/>
-      <sz val="16"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF00B050"/>
-      <sz val="16"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -203,7 +602,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="56">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -734,19 +1133,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -800,55 +1186,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -861,478 +1198,267 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="118">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="1" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" applyAlignment="1" pivotButton="1" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" pivotButton="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" pivotButton="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="justify"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="justify"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="44">
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="42"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <border>
         <left style="medium">
@@ -1341,33 +1467,17 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
-      <border>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border>
@@ -1454,11 +1564,24 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
+      <border>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <border>
@@ -1468,25 +1591,184 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" refreshedBy="Browning G Hollomon" refreshedDate="39386.43617974537" createdVersion="1" refreshedVersion="3" recordCount="137" upgradeOnRefresh="1" r:id="rId1">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Browning G Hollomon" refreshedDate="39386.436179745368" createdVersion="1" refreshedVersion="3" recordCount="137" upgradeOnRefresh="1">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:N13" sheet="SM-MD Tank Final"/>
   </cacheSource>
   <cacheFields count="15">
-    <cacheField name="Scenario Number" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="28" containsBlank="1">
+    <cacheField name="Scenario Number" numFmtId="0">
+      <sharedItems containsBlank="1" count="28">
         <m/>
         <s v="Demand Planning"/>
         <s v="FTS001"/>
@@ -1517,11 +1799,11 @@
         <s v="OTC001" u="1"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Step" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1" containsInteger="1" containsNumber="1" containsString="0" minValue="1" maxValue="46"/>
+    <cacheField name="Step" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="46"/>
     </cacheField>
-    <cacheField name="Team" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="7" containsBlank="1">
+    <cacheField name="Team" numFmtId="0">
+      <sharedItems containsBlank="1" count="7">
         <m/>
         <s v="FTS"/>
         <s v="PTP"/>
@@ -1531,35 +1813,35 @@
         <s v="XXX" u="1"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Description " uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="Description " numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="Tcode" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="Tcode" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="Tester" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="Tester" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="Test Data / Test Execution" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="Test Data / Test Execution" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="Expected Result" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="Expected Result" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="Actual Result" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="Actual Result" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="FI Impact" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="FI Impact" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="RICEF Tested" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1"/>
+    <cacheField name="RICEF Tested" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="TPR #" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1" containsNonDate="0" containsString="0"/>
+    <cacheField name="TPR #" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Status" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="34" containsBlank="1">
+    <cacheField name="Status" numFmtId="0">
+      <sharedItems containsBlank="1" count="34">
         <m/>
         <s v="50 - Pass"/>
         <s v="60 - N/A"/>
@@ -1596,13 +1878,18 @@
         <s v="20 In Process" u="1"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="User ID" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1" containsNonDate="0" containsString="0"/>
+    <cacheField name="User ID" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Comments" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsBlank="1" containsNonDate="0" containsString="0"/>
+    <cacheField name="Comments" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
   </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
 </pivotCacheDefinition>
 </file>
 
@@ -3941,231 +4228,231 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="12404" dataOnRows="1" dataCaption="Data" showError="0" showMissing="1" updatedVersion="3" minRefreshableVersion="0" asteriskTotals="0" showItems="1" editData="0" disableFieldList="0" showCalcMbrs="1" visualTotals="1" showMultipleLabel="1" showDataDropDown="1" showDrill="1" printDrill="0" showMemberPropertyTips="0" showDataTips="1" enableWizard="1" enableDrill="1" enableFieldProperties="1" preserveFormatting="1" useAutoFormatting="1" pageWrap="0" pageOverThenDown="0" subtotalHiddenItems="0" rowGrandTotals="1" colGrandTotals="1" fieldPrintTitles="0" itemPrintTitles="1" mergeItem="0" showDropZones="1" createdVersion="1" indent="0" showEmptyRow="0" showEmptyCol="0" showHeaders="1" compact="0" outline="0" outlineData="0" compactData="0" published="0" gridDropZones="1" immersive="1" multipleFieldFilters="0" chartFormat="0" fieldListSortAscending="0" mdxSubqueries="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" r:id="rId1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="3" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="1" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A3:J12" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
   <pivotFields count="15">
-    <pivotField axis="axisRow" showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1">
+    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1">
       <items count="29">
-        <item t="data" h="1" sd="1" m="1" x="27"/>
-        <item t="data" h="1" sd="1" x="0"/>
-        <item t="data" h="1" sd="1" m="1" x="10"/>
-        <item n="PP_018" t="data" sd="1" x="2"/>
-        <item t="data" sd="1" m="1" x="8"/>
-        <item t="data" sd="1" x="7"/>
-        <item t="data" sd="1" m="1" x="16"/>
-        <item t="data" sd="1" m="1" x="18"/>
-        <item t="data" sd="1" m="1" x="20"/>
-        <item t="data" sd="1" m="1" x="22"/>
-        <item t="data" sd="1" m="1" x="23"/>
-        <item t="data" sd="1" m="1" x="24"/>
-        <item t="data" sd="1" m="1" x="25"/>
-        <item t="data" sd="1" m="1" x="26"/>
-        <item t="data" sd="1" m="1" x="9"/>
-        <item t="data" sd="1" m="1" x="11"/>
-        <item t="data" sd="1" m="1" x="12"/>
-        <item t="data" sd="1" m="1" x="13"/>
-        <item t="data" sd="1" m="1" x="14"/>
-        <item t="data" sd="1" m="1" x="15"/>
-        <item t="data" sd="1" m="1" x="17"/>
-        <item t="data" sd="1" m="1" x="19"/>
-        <item t="data" sd="1" m="1" x="21"/>
-        <item t="data" sd="1" x="1"/>
-        <item t="data" sd="1" x="3"/>
-        <item t="data" sd="1" x="4"/>
-        <item t="data" sd="1" x="5"/>
-        <item t="data" sd="1" x="6"/>
-        <item t="default" sd="1"/>
+        <item h="1" m="1" x="27"/>
+        <item h="1" x="0"/>
+        <item h="1" m="1" x="10"/>
+        <item n="PP_018" x="2"/>
+        <item m="1" x="8"/>
+        <item x="7"/>
+        <item m="1" x="16"/>
+        <item m="1" x="18"/>
+        <item m="1" x="20"/>
+        <item m="1" x="22"/>
+        <item m="1" x="23"/>
+        <item m="1" x="24"/>
+        <item m="1" x="25"/>
+        <item m="1" x="26"/>
+        <item m="1" x="9"/>
+        <item m="1" x="11"/>
+        <item m="1" x="12"/>
+        <item m="1" x="13"/>
+        <item m="1" x="14"/>
+        <item m="1" x="15"/>
+        <item m="1" x="17"/>
+        <item m="1" x="19"/>
+        <item m="1" x="21"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField axis="axisRow" showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1">
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1">
       <items count="8">
-        <item t="data" h="1" sd="1" x="0"/>
-        <item t="data" sd="1" m="1" x="5"/>
-        <item t="data" sd="1" x="4"/>
-        <item t="data" sd="1" x="2"/>
-        <item n="PP" t="data" sd="1" x="1"/>
-        <item t="data" sd="1" m="1" x="6"/>
-        <item t="data" sd="1" x="3"/>
-        <item t="default" sd="1"/>
+        <item h="1" x="0"/>
+        <item m="1" x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item n="PP" x="1"/>
+        <item m="1" x="6"/>
+        <item x="3"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField axis="axisCol" dataField="1" showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1">
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField axis="axisCol" dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1">
       <items count="35">
-        <item t="data" sd="1" m="1" x="12"/>
-        <item t="data" sd="1" m="1" x="16"/>
-        <item t="data" sd="1" m="1" x="29"/>
-        <item t="data" sd="1" m="1" x="31"/>
-        <item t="data" sd="1" m="1" x="24"/>
-        <item t="data" sd="1" x="0"/>
-        <item t="data" sd="1" m="1" x="17"/>
-        <item t="data" sd="1" m="1" x="33"/>
-        <item t="data" sd="1" m="1" x="26"/>
-        <item t="data" sd="1" m="1" x="13"/>
-        <item t="data" sd="1" m="1" x="9"/>
-        <item t="data" sd="1" m="1" x="25"/>
-        <item t="data" sd="1" m="1" x="8"/>
-        <item t="data" sd="1" m="1" x="28"/>
-        <item t="data" sd="1" m="1" x="19"/>
-        <item t="data" sd="1" m="1" x="30"/>
-        <item t="data" sd="1" m="1" x="15"/>
-        <item t="data" sd="1" x="3"/>
-        <item t="data" sd="1" x="4"/>
-        <item t="data" sd="1" x="5"/>
-        <item t="data" sd="1" x="6"/>
-        <item t="data" sd="1" m="1" x="10"/>
-        <item t="data" sd="1" m="1" x="18"/>
-        <item t="data" sd="1" m="1" x="11"/>
-        <item t="data" sd="1" m="1" x="22"/>
-        <item t="data" sd="1" m="1" x="32"/>
-        <item t="data" sd="1" m="1" x="20"/>
-        <item t="data" sd="1" m="1" x="27"/>
-        <item t="data" sd="1" m="1" x="14"/>
-        <item t="data" sd="1" m="1" x="23"/>
-        <item t="data" sd="1" m="1" x="7"/>
-        <item t="data" sd="1" m="1" x="21"/>
-        <item t="data" sd="1" x="1"/>
-        <item t="data" sd="1" x="2"/>
-        <item t="default" sd="1"/>
+        <item m="1" x="12"/>
+        <item m="1" x="16"/>
+        <item m="1" x="29"/>
+        <item m="1" x="31"/>
+        <item m="1" x="24"/>
+        <item x="0"/>
+        <item m="1" x="17"/>
+        <item m="1" x="33"/>
+        <item m="1" x="26"/>
+        <item m="1" x="13"/>
+        <item m="1" x="9"/>
+        <item m="1" x="25"/>
+        <item m="1" x="8"/>
+        <item m="1" x="28"/>
+        <item m="1" x="19"/>
+        <item m="1" x="30"/>
+        <item m="1" x="15"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item m="1" x="10"/>
+        <item m="1" x="18"/>
+        <item m="1" x="11"/>
+        <item m="1" x="22"/>
+        <item m="1" x="32"/>
+        <item m="1" x="20"/>
+        <item m="1" x="27"/>
+        <item m="1" x="14"/>
+        <item m="1" x="23"/>
+        <item m="1" x="7"/>
+        <item m="1" x="21"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
-    <pivotField showDropDowns="1" compact="0" outline="0" subtotalTop="0" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" includeNewItemsInFilter="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" includeNewItemsInFilter="1"/>
   </pivotFields>
   <rowFields count="2">
     <field x="0"/>
     <field x="2"/>
   </rowFields>
   <rowItems count="8">
-    <i t="data" r="0" i="0">
+    <i>
       <x v="3"/>
       <x v="2"/>
     </i>
-    <i t="data" r="1" i="0">
+    <i r="1">
       <x v="3"/>
     </i>
-    <i t="data" r="1" i="0">
+    <i r="1">
       <x v="4"/>
     </i>
-    <i t="data" r="1" i="0">
+    <i r="1">
       <x v="6"/>
     </i>
-    <i t="default" r="0" i="0">
+    <i t="default">
       <x v="3"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="5"/>
       <x v="4"/>
     </i>
-    <i t="default" r="0" i="0">
+    <i t="default">
       <x v="5"/>
     </i>
-    <i t="grand" r="0" i="0">
-      <x v="0"/>
+    <i t="grand">
+      <x/>
     </i>
   </rowItems>
   <colFields count="1">
     <field x="12"/>
   </colFields>
   <colItems count="8">
-    <i t="data" r="0" i="0">
+    <i>
       <x v="5"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="17"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="18"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="19"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="20"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="32"/>
     </i>
-    <i t="data" r="0" i="0">
+    <i>
       <x v="33"/>
     </i>
-    <i t="grand" r="0" i="0">
-      <x v="0"/>
+    <i t="grand">
+      <x/>
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count of Status" fld="12" subtotal="count" showDataAs="normal" baseField="0" baseItem="0"/>
+    <dataField name="Count of Status" fld="12" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="44">
-    <format action="formatting" dxfId="0">
-      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0"/>
+    <format dxfId="43">
+      <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="1">
+    <format dxfId="42">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="2">
+    <format dxfId="41">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format action="formatting" dxfId="3">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="40">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="2"/>
+          <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="4">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    <format dxfId="39">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="5">
+    <format dxfId="38">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="6">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    <format dxfId="37">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="7">
-      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0"/>
+    <format dxfId="36">
+      <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="8">
+    <format dxfId="35">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="9">
+    <format dxfId="34">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format action="formatting" dxfId="10">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="33">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="2"/>
+          <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="11">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    <format dxfId="32">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="12">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    <format dxfId="31">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="13">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="14">
+    <format dxfId="29">
       <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="15">
+    <format dxfId="28">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="16">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="27">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12">
+          <reference field="12" count="5">
             <x v="6"/>
             <x v="7"/>
             <x v="8"/>
@@ -4175,10 +4462,10 @@
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="17">
-      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="26">
+      <pivotArea outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12" selected="0">
+          <reference field="12" count="5" selected="0">
             <x v="6"/>
             <x v="7"/>
             <x v="8"/>
@@ -4188,16 +4475,16 @@
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="18">
+    <format dxfId="25">
       <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="19">
+    <format dxfId="24">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="20">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="23">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12">
+          <reference field="12" count="5">
             <x v="6"/>
             <x v="7"/>
             <x v="8"/>
@@ -4207,171 +4494,171 @@
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="21">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="22">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0">
+          <reference field="0" count="1">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="22">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="21">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" defaultSubtotal="1">
+          <reference field="0" count="1" defaultSubtotal="1">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="23">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
-          <reference field="0" selected="0">
+          <reference field="0" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="2"/>
+          <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="24">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0">
+          <reference field="0" count="1">
             <x v="2"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="25">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" defaultSubtotal="1">
+          <reference field="0" count="1" defaultSubtotal="1">
             <x v="2"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="26">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="17">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
-          <reference field="0" selected="0">
+          <reference field="0" count="1" selected="0">
             <x v="2"/>
           </reference>
-          <reference field="2">
+          <reference field="2" count="1">
             <x v="1"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="27">
+    <format dxfId="16">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="28">
-      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="15">
+      <pivotArea outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" selected="0" defaultSubtotal="1">
+          <reference field="0" count="1" selected="0" defaultSubtotal="1">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="29">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" defaultSubtotal="1">
+          <reference field="0" count="1" defaultSubtotal="1">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="30">
-      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="13">
+      <pivotArea outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" selected="0" defaultSubtotal="1">
+          <reference field="0" count="1" selected="0" defaultSubtotal="1">
             <x v="3"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="31">
-      <pivotArea type="normal" dataOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="12">
+      <pivotArea outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" selected="0">
+          <reference field="0" count="1" selected="0">
             <x v="5"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="32">
+    <format dxfId="11">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="33">
+    <format dxfId="10">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="34">
+    <format dxfId="9">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format action="formatting" dxfId="35">
+    <format dxfId="8">
       <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="36">
+    <format dxfId="7">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="37">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0"/>
+          <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="38">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="0" defaultSubtotal="1">
+          <reference field="0" count="1" defaultSubtotal="1">
             <x v="3"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="39">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="4">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
-          <reference field="0" selected="0">
+          <reference field="0" count="1" selected="0">
             <x v="3"/>
           </reference>
-          <reference field="2"/>
+          <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="40">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="3">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
-          <reference field="0" selected="0">
+          <reference field="0" count="1" selected="0">
             <x v="5"/>
           </reference>
-          <reference field="2">
+          <reference field="2" count="2">
             <x v="4"/>
             <x v="6"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="41">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format action="formatting" dxfId="42">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12"/>
+          <reference field="12" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format action="formatting" dxfId="43">
-      <pivotArea type="normal" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="0">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="12"/>
+          <reference field="12" count="0"/>
         </references>
       </pivotArea>
     </format>
@@ -4666,526 +4953,511 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F70"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="25.85546875" customWidth="1" style="38" min="1" max="2"/>
-    <col width="25" customWidth="1" style="38" min="3" max="3"/>
-    <col width="25.85546875" customWidth="1" style="38" min="4" max="4"/>
-    <col width="34.85546875" customWidth="1" style="38" min="5" max="5"/>
-    <col width="40.85546875" customWidth="1" style="38" min="6" max="14"/>
-    <col width="9.140625" customWidth="1" style="38" min="15" max="16384"/>
+    <col min="1" max="2" width="25.88671875" style="38" customWidth="1"/>
+    <col min="3" max="3" width="25" style="38" customWidth="1"/>
+    <col min="4" max="4" width="25.88671875" style="38" customWidth="1"/>
+    <col min="5" max="5" width="34.88671875" style="38" customWidth="1"/>
+    <col min="6" max="14" width="40.88671875" style="38" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" style="38" customWidth="1"/>
+    <col min="16" max="16384" width="9.109375" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.1" customHeight="1" thickBot="1">
-      <c r="A1" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">__changed Owner: </t>
-        </is>
-      </c>
-      <c r="B1" s="35" t="n"/>
-      <c r="C1" s="36" t="n"/>
-      <c r="D1" s="36" t="n"/>
-      <c r="E1" s="37" t="n"/>
-    </row>
-    <row r="2" ht="14.1" customHeight="1" thickBot="1">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>Test Cycle:</t>
-        </is>
-      </c>
-      <c r="B2" s="94" t="n"/>
-      <c r="C2" s="119" t="n"/>
-      <c r="D2" s="95" t="n"/>
-      <c r="E2" s="41" t="n"/>
-    </row>
-    <row r="3" ht="12" customHeight="1">
-      <c r="A3" s="39" t="inlineStr">
-        <is>
-          <t>__changed ID:</t>
-        </is>
-      </c>
-      <c r="B3" s="120" t="inlineStr">
-        <is>
-          <t>GPO-001</t>
-        </is>
-      </c>
-      <c r="C3" s="121" t="n"/>
-      <c r="D3" s="121" t="n"/>
-      <c r="E3" s="122" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="39" t="inlineStr">
-        <is>
-          <t>Test Objective:</t>
-        </is>
-      </c>
-      <c r="B4" s="120" t="inlineStr">
-        <is>
-          <t>Create PR and PO in guided buying.</t>
-        </is>
-      </c>
-      <c r="C4" s="121" t="n"/>
-      <c r="D4" s="121" t="n"/>
-      <c r="E4" s="122" t="n"/>
-    </row>
-    <row r="5" ht="12" customHeight="1">
-      <c r="A5" s="123" t="inlineStr">
-        <is>
-          <t>__changed Description:</t>
-        </is>
-      </c>
-      <c r="B5" s="103" t="n"/>
-      <c r="E5" s="124" t="n"/>
-    </row>
-    <row r="6" ht="14.1" customHeight="1" thickBot="1">
-      <c r="A6" s="125" t="n"/>
-      <c r="B6" s="126" t="n"/>
-      <c r="C6" s="126" t="n"/>
-      <c r="D6" s="126" t="n"/>
-      <c r="E6" s="127" t="n"/>
-    </row>
-    <row r="7" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A7" s="42" t="n"/>
-      <c r="E7" s="43" t="n"/>
-    </row>
-    <row r="8" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A8" s="123" t="inlineStr">
-        <is>
-          <t>Long Description __changed Summary for items to be tested</t>
-        </is>
-      </c>
-      <c r="B8" s="128" t="n"/>
-      <c r="C8" s="128" t="n"/>
-      <c r="D8" s="128" t="n"/>
-      <c r="E8" s="129" t="n"/>
-    </row>
-    <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="130" t="inlineStr">
-        <is>
-          <t>Search catalog for items
-Add items to cart
-Complete requisition details and submit
-Review PR approval flow 
-Confirm PO generation
-Create associated receipt</t>
-        </is>
-      </c>
-      <c r="B9" s="131" t="n"/>
-      <c r="C9" s="131" t="n"/>
-      <c r="D9" s="131" t="n"/>
-      <c r="E9" s="132" t="n"/>
-    </row>
-    <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="133" t="n"/>
-      <c r="E10" s="124" t="n"/>
-    </row>
-    <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="133" t="n"/>
-      <c r="E11" s="124" t="n"/>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="133" t="n"/>
-      <c r="E12" s="124" t="n"/>
-      <c r="F12" s="38" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="133" t="n"/>
-      <c r="E13" s="124" t="n"/>
-    </row>
-    <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="133" t="n"/>
-      <c r="E14" s="124" t="n"/>
-    </row>
-    <row r="15" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A15" s="133" t="n"/>
-      <c r="E15" s="124" t="n"/>
-    </row>
-    <row r="16" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A16" s="44" t="inlineStr">
-        <is>
-          <t>Data Requirements</t>
-        </is>
-      </c>
-      <c r="B16" s="45" t="inlineStr">
-        <is>
-          <t>Legacy Reference</t>
-        </is>
-      </c>
-      <c r="C16" s="45" t="inlineStr">
-        <is>
-          <t>SAP Reference</t>
-        </is>
-      </c>
-      <c r="D16" s="45" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="E16" s="46" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="69" t="n"/>
-      <c r="B17" s="111" t="n"/>
-      <c r="C17" s="93" t="n"/>
-      <c r="D17" s="134" t="n"/>
-      <c r="E17" s="132" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="67" t="n"/>
-      <c r="B18" s="93" t="n"/>
-      <c r="C18" s="93" t="n"/>
-      <c r="D18" s="133" t="n"/>
-      <c r="E18" s="124" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="68" t="n"/>
-      <c r="B19" s="93" t="n"/>
-      <c r="C19" s="93" t="n"/>
-      <c r="D19" s="133" t="n"/>
-      <c r="E19" s="124" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="93" t="n"/>
-      <c r="C20" s="93" t="n"/>
-      <c r="D20" s="133" t="n"/>
-      <c r="E20" s="124" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="50" t="n"/>
-      <c r="C21" s="93" t="n"/>
-      <c r="D21" s="133" t="n"/>
-      <c r="E21" s="124" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="110" t="n"/>
-      <c r="B22" s="111" t="n"/>
-      <c r="C22" s="93" t="n"/>
-      <c r="D22" s="133" t="n"/>
-      <c r="E22" s="124" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="110" t="n"/>
-      <c r="B23" s="111" t="n"/>
-      <c r="C23" s="93" t="n"/>
-      <c r="D23" s="133" t="n"/>
-      <c r="E23" s="124" t="n"/>
-    </row>
-    <row r="24" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A24" s="51" t="n"/>
-      <c r="D24" s="133" t="n"/>
-      <c r="E24" s="124" t="n"/>
-    </row>
-    <row r="25" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A25" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prerequisite </t>
-        </is>
-      </c>
-      <c r="B25" s="45" t="n"/>
-      <c r="C25" s="45" t="n"/>
-      <c r="D25" s="45" t="n"/>
-      <c r="E25" s="46" t="n"/>
-    </row>
-    <row r="26" ht="12" customHeight="1">
-      <c r="A26" s="92" t="n"/>
-      <c r="E26" s="43" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="92" t="n"/>
-      <c r="E27" s="43" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="92" t="n"/>
-      <c r="E28" s="43" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="92" t="n"/>
-      <c r="E29" s="43" t="n"/>
-    </row>
-    <row r="30" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A30" s="51" t="n"/>
-      <c r="E30" s="43" t="n"/>
-    </row>
-    <row r="31" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="44" t="inlineStr">
-        <is>
-          <t>Key RICEF Objects</t>
-        </is>
-      </c>
-      <c r="B31" s="45" t="n"/>
-      <c r="C31" s="45" t="n"/>
-      <c r="D31" s="45" t="n"/>
-      <c r="E31" s="46" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="92" t="inlineStr">
-        <is>
-          <t>Master Data Validation</t>
-        </is>
-      </c>
-      <c r="E32" s="43" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="92" t="inlineStr">
-        <is>
-          <t>SAP PO Post and Validation</t>
-        </is>
-      </c>
-      <c r="E33" s="43" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="92" t="inlineStr">
-        <is>
-          <t>SAP Invoice to SAP</t>
-        </is>
-      </c>
-      <c r="E34" s="43" t="n"/>
-    </row>
-    <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="92" t="inlineStr">
-        <is>
-          <t>Payment Remitance Validation to Ariba</t>
-        </is>
-      </c>
-      <c r="E35" s="52" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="90" t="n"/>
-      <c r="C36" s="91" t="n"/>
-      <c r="E36" s="43" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="90" t="n"/>
-      <c r="C37" s="91" t="n"/>
-      <c r="E37" s="43" t="n"/>
-    </row>
-    <row r="38" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A38" s="53" t="inlineStr">
-        <is>
-          <t>TEST SRIPT &amp; EXECUTION APPROVAL</t>
-        </is>
-      </c>
-      <c r="E38" s="43" t="n"/>
-    </row>
-    <row r="39" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A39" s="54" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B39" s="55" t="inlineStr">
-        <is>
-          <t>Signature</t>
-        </is>
-      </c>
-      <c r="C39" s="55" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D39" s="55" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="E39" s="46" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="107" t="n"/>
-      <c r="B40" s="108" t="n"/>
-      <c r="C40" s="108" t="n"/>
-      <c r="D40" s="108" t="n"/>
-      <c r="E40" s="58" t="n"/>
-    </row>
-    <row r="41" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A41" s="59" t="n"/>
-      <c r="B41" s="60" t="n"/>
-      <c r="C41" s="60" t="n"/>
-      <c r="D41" s="60" t="n"/>
-      <c r="E41" s="61" t="n"/>
-    </row>
-    <row r="42"/>
-    <row r="43" ht="12.75" customHeight="1"/>
-    <row r="44" ht="12.75" customHeight="1"/>
-    <row r="45" ht="12" customHeight="1"/>
-    <row r="46"/>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="62" t="n"/>
-      <c r="B47" s="63" t="n"/>
-      <c r="C47" s="63" t="n"/>
-      <c r="D47" s="63" t="n"/>
-    </row>
-    <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="62" t="n"/>
-      <c r="B48" s="63" t="n"/>
-      <c r="C48" s="63" t="n"/>
-      <c r="D48" s="63" t="n"/>
-    </row>
-    <row r="49" ht="12.75" customHeight="1">
-      <c r="A49" s="64" t="n"/>
-      <c r="B49" s="65" t="n"/>
-      <c r="C49" s="66" t="n"/>
-      <c r="D49" s="65" t="n"/>
-      <c r="E49" s="65" t="n"/>
-    </row>
-    <row r="50" ht="12.75" customHeight="1">
-      <c r="A50" s="63" t="n"/>
-      <c r="B50" s="63" t="n"/>
-      <c r="C50" s="63" t="n"/>
-      <c r="D50" s="63" t="n"/>
-    </row>
-    <row r="51" ht="12.75" customHeight="1">
-      <c r="A51" s="63" t="n"/>
-      <c r="B51" s="63" t="n"/>
-      <c r="C51" s="63" t="n"/>
-      <c r="D51" s="63" t="n"/>
-    </row>
-    <row r="52" ht="12.75" customHeight="1">
-      <c r="A52" s="63" t="n"/>
-      <c r="B52" s="63" t="n"/>
-      <c r="C52" s="63" t="n"/>
-      <c r="D52" s="63" t="n"/>
-    </row>
-    <row r="53" ht="12.75" customHeight="1">
-      <c r="A53" s="63" t="n"/>
-      <c r="B53" s="63" t="n"/>
-      <c r="C53" s="63" t="n"/>
-      <c r="D53" s="63" t="n"/>
-    </row>
-    <row r="54" ht="12.75" customHeight="1">
-      <c r="A54" s="63" t="n"/>
-      <c r="B54" s="63" t="n"/>
-      <c r="C54" s="63" t="n"/>
-      <c r="D54" s="63" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="62" t="n"/>
-      <c r="B55" s="63" t="n"/>
-      <c r="C55" s="63" t="n"/>
-      <c r="D55" s="63" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="62" t="n"/>
-      <c r="B56" s="63" t="n"/>
-      <c r="C56" s="63" t="n"/>
-      <c r="D56" s="63" t="n"/>
-    </row>
-    <row r="57" ht="12.75" customHeight="1">
-      <c r="A57" s="63" t="n"/>
-      <c r="B57" s="63" t="n"/>
-      <c r="C57" s="63" t="n"/>
-      <c r="D57" s="63" t="n"/>
-      <c r="E57" s="63" t="n"/>
-    </row>
-    <row r="58" ht="12.75" customHeight="1">
-      <c r="A58" s="63" t="n"/>
-      <c r="B58" s="63" t="n"/>
-      <c r="C58" s="63" t="n"/>
-      <c r="D58" s="63" t="n"/>
-      <c r="E58" s="63" t="n"/>
-    </row>
-    <row r="59" ht="12.75" customHeight="1">
-      <c r="A59" s="63" t="n"/>
-      <c r="B59" s="63" t="n"/>
-      <c r="C59" s="63" t="n"/>
-      <c r="D59" s="63" t="n"/>
-      <c r="E59" s="63" t="n"/>
-    </row>
-    <row r="60" ht="12.75" customHeight="1">
-      <c r="A60" s="63" t="n"/>
-      <c r="B60" s="63" t="n"/>
-      <c r="C60" s="63" t="n"/>
-      <c r="D60" s="63" t="n"/>
-      <c r="E60" s="63" t="n"/>
-    </row>
-    <row r="61" ht="12.75" customHeight="1">
-      <c r="A61" s="63" t="n"/>
-      <c r="B61" s="63" t="n"/>
-      <c r="C61" s="63" t="n"/>
-      <c r="D61" s="63" t="n"/>
-      <c r="E61" s="63" t="n"/>
-    </row>
-    <row r="62" ht="12.75" customHeight="1">
-      <c r="A62" s="63" t="n"/>
-      <c r="B62" s="63" t="n"/>
-      <c r="C62" s="63" t="n"/>
-      <c r="D62" s="63" t="n"/>
-      <c r="E62" s="63" t="n"/>
-    </row>
-    <row r="63" ht="12.75" customHeight="1">
-      <c r="A63" s="63" t="n"/>
-      <c r="B63" s="63" t="n"/>
-      <c r="C63" s="63" t="n"/>
-      <c r="D63" s="63" t="n"/>
-      <c r="E63" s="63" t="n"/>
-    </row>
-    <row r="64" ht="12.75" customHeight="1">
-      <c r="A64" s="63" t="n"/>
-      <c r="B64" s="63" t="n"/>
-      <c r="C64" s="63" t="n"/>
-      <c r="D64" s="63" t="n"/>
-      <c r="E64" s="63" t="n"/>
-    </row>
-    <row r="65" ht="12.75" customHeight="1">
-      <c r="A65" s="63" t="n"/>
-      <c r="B65" s="63" t="n"/>
-      <c r="C65" s="63" t="n"/>
-      <c r="D65" s="63" t="n"/>
-      <c r="E65" s="63" t="n"/>
-    </row>
-    <row r="66" ht="12.75" customHeight="1">
-      <c r="A66" s="63" t="n"/>
-      <c r="B66" s="63" t="n"/>
-      <c r="C66" s="63" t="n"/>
-      <c r="D66" s="63" t="n"/>
-      <c r="E66" s="63" t="n"/>
-    </row>
-    <row r="67" ht="12.75" customHeight="1">
-      <c r="A67" s="63" t="n"/>
-      <c r="B67" s="63" t="n"/>
-      <c r="C67" s="63" t="n"/>
-      <c r="D67" s="63" t="n"/>
-      <c r="E67" s="63" t="n"/>
-    </row>
-    <row r="68" ht="12.75" customHeight="1">
-      <c r="A68" s="63" t="n"/>
-      <c r="B68" s="63" t="n"/>
-      <c r="C68" s="63" t="n"/>
-      <c r="D68" s="63" t="n"/>
-      <c r="E68" s="63" t="n"/>
-    </row>
-    <row r="69" ht="12.75" customHeight="1">
-      <c r="A69" s="63" t="n"/>
-      <c r="B69" s="63" t="n"/>
-      <c r="C69" s="63" t="n"/>
-      <c r="D69" s="63" t="n"/>
-      <c r="E69" s="63" t="n"/>
-    </row>
-    <row r="70" ht="12.75" customHeight="1">
-      <c r="A70" s="63" t="n"/>
-      <c r="B70" s="63" t="n"/>
-      <c r="C70" s="63" t="n"/>
-      <c r="D70" s="63" t="n"/>
-      <c r="E70" s="63" t="n"/>
+    <row r="1" spans="1:6" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="37"/>
+    </row>
+    <row r="2" spans="1:6" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="99"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="40"/>
+    </row>
+    <row r="3" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="101" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="103"/>
+    </row>
+    <row r="4" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A4" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="101" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="103"/>
+    </row>
+    <row r="5" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="104" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="109"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="97"/>
+    </row>
+    <row r="6" spans="1:6" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="105"/>
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="111"/>
+    </row>
+    <row r="7" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="41"/>
+      <c r="E7" s="42"/>
+    </row>
+    <row r="8" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="104" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="108"/>
+    </row>
+    <row r="9" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="93" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="94"/>
+      <c r="C9" s="94"/>
+      <c r="D9" s="94"/>
+      <c r="E9" s="95"/>
+    </row>
+    <row r="10" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="96"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="97"/>
+    </row>
+    <row r="11" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="96"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="91"/>
+      <c r="E11" s="97"/>
+    </row>
+    <row r="12" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="96"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="91"/>
+      <c r="E12" s="97"/>
+      <c r="F12" s="38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="96"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="91"/>
+      <c r="E13" s="97"/>
+    </row>
+    <row r="14" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="96"/>
+      <c r="B14" s="91"/>
+      <c r="C14" s="91"/>
+      <c r="D14" s="91"/>
+      <c r="E14" s="97"/>
+    </row>
+    <row r="15" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="96"/>
+      <c r="B15" s="91"/>
+      <c r="C15" s="91"/>
+      <c r="D15" s="91"/>
+      <c r="E15" s="97"/>
+    </row>
+    <row r="16" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="45"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="63"/>
+      <c r="B17" s="88"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="98"/>
+      <c r="E17" s="95"/>
+    </row>
+    <row r="18" spans="1:5" ht="12" x14ac:dyDescent="0.25">
+      <c r="A18" s="61"/>
+      <c r="B18" s="83"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="96"/>
+      <c r="E18" s="97"/>
+    </row>
+    <row r="19" spans="1:5" ht="12" x14ac:dyDescent="0.25">
+      <c r="A19" s="62"/>
+      <c r="B19" s="83"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="96"/>
+      <c r="E19" s="97"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="97"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B21" s="46"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="96"/>
+      <c r="E21" s="97"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="87"/>
+      <c r="B22" s="88"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="96"/>
+      <c r="E22" s="97"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="87"/>
+      <c r="B23" s="88"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="96"/>
+      <c r="E23" s="97"/>
+    </row>
+    <row r="24" spans="1:5" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="47"/>
+      <c r="D24" s="96"/>
+      <c r="E24" s="97"/>
+    </row>
+    <row r="25" spans="1:5" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="45"/>
+    </row>
+    <row r="26" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="90"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="91"/>
+      <c r="D26" s="91"/>
+      <c r="E26" s="42"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="90"/>
+      <c r="B27" s="91"/>
+      <c r="C27" s="91"/>
+      <c r="D27" s="91"/>
+      <c r="E27" s="42"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="90"/>
+      <c r="B28" s="91"/>
+      <c r="C28" s="91"/>
+      <c r="D28" s="91"/>
+      <c r="E28" s="42"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="90"/>
+      <c r="B29" s="91"/>
+      <c r="C29" s="91"/>
+      <c r="D29" s="91"/>
+      <c r="E29" s="42"/>
+    </row>
+    <row r="30" spans="1:5" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="47"/>
+      <c r="E30" s="42"/>
+    </row>
+    <row r="31" spans="1:5" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="44"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="45"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="90" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="91"/>
+      <c r="C32" s="91"/>
+      <c r="D32" s="91"/>
+      <c r="E32" s="42"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="90" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="91"/>
+      <c r="C33" s="91"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="42"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="90" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="91"/>
+      <c r="C34" s="91"/>
+      <c r="D34" s="91"/>
+      <c r="E34" s="42"/>
+    </row>
+    <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="90" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="91"/>
+      <c r="C35" s="91"/>
+      <c r="D35" s="91"/>
+      <c r="E35" s="48"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="92"/>
+      <c r="B36" s="91"/>
+      <c r="C36" s="106"/>
+      <c r="D36" s="91"/>
+      <c r="E36" s="42"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="92"/>
+      <c r="B37" s="91"/>
+      <c r="C37" s="106"/>
+      <c r="D37" s="91"/>
+      <c r="E37" s="42"/>
+    </row>
+    <row r="38" spans="1:5" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="42"/>
+    </row>
+    <row r="39" spans="1:5" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="45"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="85"/>
+      <c r="B40" s="86"/>
+      <c r="C40" s="86"/>
+      <c r="D40" s="86"/>
+      <c r="E40" s="52"/>
+    </row>
+    <row r="41" spans="1:5" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="53"/>
+      <c r="B41" s="54"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="55"/>
+    </row>
+    <row r="43" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="56"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+    </row>
+    <row r="48" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="56"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+    </row>
+    <row r="49" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="58"/>
+      <c r="B49" s="59"/>
+      <c r="C49" s="60"/>
+      <c r="D49" s="59"/>
+      <c r="E49" s="59"/>
+    </row>
+    <row r="50" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="57"/>
+      <c r="B50" s="57"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="57"/>
+    </row>
+    <row r="51" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="57"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="57"/>
+      <c r="D51" s="57"/>
+    </row>
+    <row r="52" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="57"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="57"/>
+    </row>
+    <row r="53" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="57"/>
+      <c r="B53" s="57"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="57"/>
+    </row>
+    <row r="54" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="57"/>
+      <c r="B54" s="57"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="57"/>
+    </row>
+    <row r="55" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="56"/>
+      <c r="B55" s="57"/>
+      <c r="C55" s="57"/>
+      <c r="D55" s="57"/>
+    </row>
+    <row r="56" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="56"/>
+      <c r="B56" s="57"/>
+      <c r="C56" s="57"/>
+      <c r="D56" s="57"/>
+    </row>
+    <row r="57" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="57"/>
+      <c r="B57" s="57"/>
+      <c r="C57" s="57"/>
+      <c r="D57" s="57"/>
+      <c r="E57" s="57"/>
+    </row>
+    <row r="58" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="57"/>
+      <c r="B58" s="57"/>
+      <c r="C58" s="57"/>
+      <c r="D58" s="57"/>
+      <c r="E58" s="57"/>
+    </row>
+    <row r="59" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="57"/>
+      <c r="B59" s="57"/>
+      <c r="C59" s="57"/>
+      <c r="D59" s="57"/>
+      <c r="E59" s="57"/>
+    </row>
+    <row r="60" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="57"/>
+      <c r="B60" s="57"/>
+      <c r="C60" s="57"/>
+      <c r="D60" s="57"/>
+      <c r="E60" s="57"/>
+    </row>
+    <row r="61" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="57"/>
+      <c r="B61" s="57"/>
+      <c r="C61" s="57"/>
+      <c r="D61" s="57"/>
+      <c r="E61" s="57"/>
+    </row>
+    <row r="62" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="57"/>
+      <c r="B62" s="57"/>
+      <c r="C62" s="57"/>
+      <c r="D62" s="57"/>
+      <c r="E62" s="57"/>
+    </row>
+    <row r="63" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="57"/>
+      <c r="B63" s="57"/>
+      <c r="C63" s="57"/>
+      <c r="D63" s="57"/>
+      <c r="E63" s="57"/>
+    </row>
+    <row r="64" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="57"/>
+      <c r="B64" s="57"/>
+      <c r="C64" s="57"/>
+      <c r="D64" s="57"/>
+      <c r="E64" s="57"/>
+    </row>
+    <row r="65" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="57"/>
+      <c r="B65" s="57"/>
+      <c r="C65" s="57"/>
+      <c r="D65" s="57"/>
+      <c r="E65" s="57"/>
+    </row>
+    <row r="66" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="57"/>
+      <c r="B66" s="57"/>
+      <c r="C66" s="57"/>
+      <c r="D66" s="57"/>
+      <c r="E66" s="57"/>
+    </row>
+    <row r="67" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="57"/>
+      <c r="B67" s="57"/>
+      <c r="C67" s="57"/>
+      <c r="D67" s="57"/>
+      <c r="E67" s="57"/>
+    </row>
+    <row r="68" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="57"/>
+      <c r="B68" s="57"/>
+      <c r="C68" s="57"/>
+      <c r="D68" s="57"/>
+      <c r="E68" s="57"/>
+    </row>
+    <row r="69" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="57"/>
+      <c r="B69" s="57"/>
+      <c r="C69" s="57"/>
+      <c r="D69" s="57"/>
+      <c r="E69" s="57"/>
+    </row>
+    <row r="70" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="57"/>
+      <c r="B70" s="57"/>
+      <c r="C70" s="57"/>
+      <c r="D70" s="57"/>
+      <c r="E70" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A9:E15"/>
-    <mergeCell ref="D17:E24"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="A34:D34"/>
@@ -5200,1207 +5472,918 @@
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:E15"/>
+    <mergeCell ref="D17:E24"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D2:E2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:E2">
       <formula1>"R4-Cycle 1,R4-Cycle 2,R4-Cycle 3,R4-Cycle 4,R4-Regression Test,R4-Business Simulation"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" scale="69"/>
+  <pageSetup scale="69" orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q26"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="35.7109375" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="35.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="10.28515625" customWidth="1" style="87" min="1" max="1"/>
-    <col width="18.7109375" customWidth="1" style="87" min="2" max="2"/>
-    <col width="10.28515625" customWidth="1" style="72" min="3" max="3"/>
-    <col width="15.7109375" bestFit="1" customWidth="1" style="72" min="4" max="4"/>
-    <col width="14" customWidth="1" style="87" min="5" max="5"/>
-    <col width="80.42578125" customWidth="1" style="88" min="6" max="6"/>
-    <col width="14.140625" customWidth="1" style="88" min="7" max="7"/>
-    <col width="62.42578125" customWidth="1" style="72" min="8" max="8"/>
-    <col width="46.42578125" customWidth="1" style="72" min="9" max="9"/>
-    <col width="15.85546875" customWidth="1" style="72" min="10" max="10"/>
-    <col width="25.28515625" bestFit="1" customWidth="1" style="72" min="11" max="11"/>
-    <col width="18.85546875" customWidth="1" style="87" min="12" max="12"/>
-    <col width="18.7109375" customWidth="1" style="72" min="13" max="13"/>
-    <col width="17.42578125" customWidth="1" style="72" min="14" max="14"/>
-    <col width="16.42578125" customWidth="1" style="88" min="15" max="15"/>
-    <col width="13.28515625" customWidth="1" style="88" min="16" max="16"/>
-    <col width="37.140625" bestFit="1" customWidth="1" style="72" min="17" max="17"/>
-    <col width="9.140625" customWidth="1" style="72" min="18" max="18"/>
-    <col width="35.7109375" customWidth="1" style="72" min="19" max="16384"/>
+    <col min="1" max="1" width="10.33203125" style="80" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="80" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="65" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" style="65" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="80" customWidth="1"/>
+    <col min="6" max="6" width="80.44140625" style="81" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" style="81" customWidth="1"/>
+    <col min="8" max="8" width="62.44140625" style="65" customWidth="1"/>
+    <col min="9" max="9" width="46.44140625" style="65" customWidth="1"/>
+    <col min="10" max="10" width="15.88671875" style="65" customWidth="1"/>
+    <col min="11" max="11" width="25.33203125" style="65" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.88671875" style="80" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" style="65" customWidth="1"/>
+    <col min="14" max="14" width="17.44140625" style="65" customWidth="1"/>
+    <col min="15" max="15" width="16.44140625" style="81" customWidth="1"/>
+    <col min="16" max="16" width="13.33203125" style="81" customWidth="1"/>
+    <col min="17" max="17" width="37.109375" style="65" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.109375" style="65" customWidth="1"/>
+    <col min="19" max="19" width="35.6640625" style="65" customWidth="1"/>
+    <col min="20" max="16384" width="35.6640625" style="65"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="116" t="inlineStr">
-        <is>
-          <t>__changed Number</t>
-        </is>
-      </c>
-      <c r="B1" s="116" t="n"/>
-      <c r="C1" s="116" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D1" s="116" t="n"/>
-      <c r="E1" s="116" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="F1" s="116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Description </t>
-        </is>
-      </c>
-      <c r="G1" s="116" t="inlineStr">
-        <is>
-          <t>Tcode</t>
-        </is>
-      </c>
-      <c r="H1" s="116" t="inlineStr">
-        <is>
-          <t>Test Data / Test Execution</t>
-        </is>
-      </c>
-      <c r="I1" s="116" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="J1" s="117" t="inlineStr">
-        <is>
-          <t>Step Completed
-Sucessfullyåç</t>
-        </is>
-      </c>
-      <c r="K1" s="116" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="L1" s="116" t="inlineStr">
-        <is>
-          <t>FI Impact</t>
-        </is>
-      </c>
-      <c r="M1" s="116" t="inlineStr">
-        <is>
-          <t>RICEF Tested</t>
-        </is>
-      </c>
-      <c r="N1" s="116" t="inlineStr">
-        <is>
-          <t>TPR #</t>
-        </is>
-      </c>
-      <c r="O1" s="116" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="P1" s="118" t="inlineStr">
-        <is>
-          <t>Tester/User ID</t>
-        </is>
-      </c>
-      <c r="Q1" s="116" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="135" t="n"/>
-      <c r="B2" s="116" t="n"/>
-      <c r="C2" s="135" t="n"/>
-      <c r="D2" s="73" t="n"/>
-      <c r="E2" s="135" t="n"/>
-      <c r="F2" s="135" t="n"/>
-      <c r="G2" s="135" t="n"/>
-      <c r="H2" s="135" t="n"/>
-      <c r="I2" s="135" t="n"/>
-      <c r="J2" s="136" t="n"/>
-      <c r="K2" s="135" t="n"/>
-      <c r="L2" s="73" t="inlineStr">
-        <is>
-          <t>Y or N</t>
-        </is>
-      </c>
-      <c r="M2" s="135" t="n"/>
-      <c r="N2" s="135" t="n"/>
-      <c r="O2" s="135" t="n"/>
-      <c r="P2" s="137" t="n"/>
-      <c r="Q2" s="135" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="74" t="n"/>
-      <c r="B3" s="74" t="inlineStr">
-        <is>
-          <t>__changed No.</t>
-        </is>
-      </c>
-      <c r="C3" s="74" t="n"/>
-      <c r="D3" s="74" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="E3" s="74" t="n"/>
-      <c r="F3" s="75" t="n"/>
-      <c r="G3" s="76" t="n"/>
-      <c r="H3" s="76" t="n"/>
-      <c r="I3" s="76" t="n"/>
-      <c r="J3" s="76" t="n"/>
-      <c r="K3" s="74" t="n"/>
-      <c r="L3" s="74" t="n"/>
-      <c r="M3" s="74" t="n"/>
-      <c r="N3" s="74" t="n"/>
-      <c r="O3" s="77" t="n"/>
-      <c r="P3" s="77" t="n"/>
-      <c r="Q3" s="74" t="n"/>
-    </row>
-    <row r="4" ht="37.5" customFormat="1" customHeight="1" s="81">
-      <c r="A4" s="70" t="inlineStr">
-        <is>
-          <t>BL_001</t>
-        </is>
-      </c>
-      <c r="B4" s="70" t="inlineStr">
-        <is>
-          <t>GPO-001</t>
-        </is>
-      </c>
-      <c r="C4" s="70">
-        <f>ROW(A4)-3</f>
-        <v/>
-      </c>
-      <c r="D4" s="70" t="inlineStr">
-        <is>
-          <t>env</t>
-        </is>
-      </c>
-      <c r="E4" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F4" s="70" t="inlineStr">
-        <is>
-          <t>Complete script GEN-001 to log into Guided Buying.</t>
-        </is>
-      </c>
-      <c r="G4" s="70" t="n"/>
-      <c r="H4" s="78" t="inlineStr">
-        <is>
-          <t>Login
-Password</t>
-        </is>
-      </c>
-      <c r="I4" s="79" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Nexus Water Group homepage is presented. </t>
-        </is>
-      </c>
-      <c r="J4" s="80" t="b">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="112" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="89"/>
+      <c r="C1" s="112" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="89"/>
+      <c r="E1" s="112" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="112" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="114" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="112" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="89" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" s="112" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1" s="112" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="112" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" s="116" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" s="112" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="113"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="115"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="66" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="113"/>
+      <c r="P2" s="117"/>
+      <c r="Q2" s="113"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="67"/>
+      <c r="B3" s="67" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="67"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="70"/>
+      <c r="P3" s="70"/>
+      <c r="Q3" s="67"/>
+    </row>
+    <row r="4" spans="1:17" s="74" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="64">
+        <f t="shared" ref="C4:C26" si="0">ROW(A4)-3</f>
+        <v>1</v>
+      </c>
+      <c r="D4" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="64"/>
+      <c r="H4" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="72" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K4" s="70" t="n"/>
-      <c r="L4" s="70" t="n"/>
-      <c r="M4" s="70" t="n"/>
-      <c r="N4" s="70" t="n"/>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="70" t="n"/>
-      <c r="Q4" s="70" t="n"/>
-    </row>
-    <row r="5" ht="65.25" customFormat="1" customHeight="1" s="81">
-      <c r="A5" s="70" t="n"/>
-      <c r="B5" s="70" t="n"/>
-      <c r="C5" s="70">
-        <f>ROW(A5)-3</f>
-        <v/>
-      </c>
-      <c r="D5" s="70" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="E5" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F5" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_enter_ search term In the box containing the message "Find goods and services", search for a catalog item by name.
-Click on Magnifying glass after entering the item name on box. </t>
-        </is>
-      </c>
-      <c r="G5" s="70" t="n"/>
-      <c r="H5" s="78" t="inlineStr">
-        <is>
-          <t>"goggles"</t>
-        </is>
-      </c>
-      <c r="I5" s="70" t="inlineStr">
-        <is>
-          <t>Search results from the  company catalog are  displayed.</t>
-        </is>
-      </c>
-      <c r="J5" s="80" t="b">
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+    </row>
+    <row r="5" spans="1:17" s="74" customFormat="1" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D5" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="64"/>
+      <c r="H5" s="71" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K5" s="70" t="n"/>
-      <c r="L5" s="70" t="n"/>
-      <c r="M5" s="70" t="n"/>
-      <c r="N5" s="70" t="n"/>
-      <c r="O5" s="70" t="n"/>
-      <c r="P5" s="70" t="n"/>
-      <c r="Q5" s="70" t="n"/>
-    </row>
-    <row r="6" ht="33.75" customFormat="1" customHeight="1" s="81">
-      <c r="A6" s="70" t="n"/>
-      <c r="B6" s="70" t="n"/>
-      <c r="C6" s="70">
-        <f>ROW(A6)-3</f>
-        <v/>
-      </c>
-      <c r="D6" s="70" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="E6" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F6" s="70" t="inlineStr">
-        <is>
-          <t>Hover on the desired item.</t>
-        </is>
-      </c>
-      <c r="G6" s="70" t="n"/>
-      <c r="H6" s="78" t="n"/>
-      <c r="I6" s="70" t="n"/>
-      <c r="J6" s="80" t="b">
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="64"/>
+      <c r="Q5" s="64"/>
+    </row>
+    <row r="6" spans="1:17" s="74" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="64"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="D6" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="64"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K6" s="70" t="n"/>
-      <c r="L6" s="70" t="n"/>
-      <c r="M6" s="70" t="n"/>
-      <c r="N6" s="70" t="n"/>
-      <c r="O6" s="70" t="n"/>
-      <c r="P6" s="70" t="n"/>
-      <c r="Q6" s="70" t="n"/>
-    </row>
-    <row r="7" ht="37.5" customFormat="1" customHeight="1" s="81">
-      <c r="A7" s="70" t="n"/>
-      <c r="B7" s="70" t="n"/>
-      <c r="C7" s="70">
-        <f>ROW(A7)-3</f>
-        <v/>
-      </c>
-      <c r="D7" s="70" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="E7" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F7" s="70" t="inlineStr">
-        <is>
-          <t>Use the +/- buttons to increase or decrease the quantity.</t>
-        </is>
-      </c>
-      <c r="G7" s="70" t="n"/>
-      <c r="H7" s="78" t="inlineStr">
-        <is>
-          <t>Safety Goggles - Pro-Safe - Direct Ventilation
-$3.49 USD / each</t>
-        </is>
-      </c>
-      <c r="I7" s="70" t="inlineStr">
-        <is>
-          <t>Quantity can be increased or decreased as desired.</t>
-        </is>
-      </c>
-      <c r="J7" s="80" t="b">
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="64"/>
+      <c r="P6" s="64"/>
+      <c r="Q6" s="64"/>
+    </row>
+    <row r="7" spans="1:17" s="74" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="64"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D7" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="64"/>
+      <c r="H7" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" s="64" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K7" s="70" t="n"/>
-      <c r="L7" s="70" t="n"/>
-      <c r="M7" s="70" t="n"/>
-      <c r="N7" s="70" t="n"/>
-      <c r="O7" s="70" t="n"/>
-      <c r="P7" s="70" t="n"/>
-      <c r="Q7" s="70" t="n"/>
-    </row>
-    <row r="8" ht="39.75" customFormat="1" customHeight="1" s="81">
-      <c r="A8" s="70" t="n"/>
-      <c r="B8" s="70" t="n"/>
-      <c r="C8" s="70">
-        <f>ROW(A8)-3</f>
-        <v/>
-      </c>
-      <c r="D8" s="70" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="E8" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F8" s="70" t="inlineStr">
-        <is>
-          <t>_enter_ the desired quantity  in the "Qty" box.</t>
-        </is>
-      </c>
-      <c r="G8" s="70" t="n"/>
-      <c r="H8" s="78" t="inlineStr">
-        <is>
-          <t>Quantity: 30</t>
-        </is>
-      </c>
-      <c r="I8" s="70" t="inlineStr">
-        <is>
-          <t>Desired quantity is indicated.</t>
-        </is>
-      </c>
-      <c r="J8" s="80" t="b">
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="64"/>
+    </row>
+    <row r="8" spans="1:17" s="74" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="64"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D8" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="64" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="64"/>
+      <c r="H8" s="71" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K8" s="70" t="n"/>
-      <c r="L8" s="70" t="n"/>
-      <c r="M8" s="70" t="n"/>
-      <c r="N8" s="70" t="n"/>
-      <c r="O8" s="70" t="n"/>
-      <c r="P8" s="70" t="n"/>
-      <c r="Q8" s="70" t="n"/>
-    </row>
-    <row r="9" ht="36" customFormat="1" customHeight="1" s="81">
-      <c r="A9" s="70" t="n"/>
-      <c r="B9" s="70" t="n"/>
-      <c r="C9" s="70">
-        <f>ROW(A9)-3</f>
-        <v/>
-      </c>
-      <c r="D9" s="70" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="E9" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F9" s="70" t="inlineStr">
-        <is>
-          <t>Press "Add to Cart" button.</t>
-        </is>
-      </c>
-      <c r="G9" s="70" t="n"/>
-      <c r="H9" s="70" t="n"/>
-      <c r="I9" s="70" t="inlineStr">
-        <is>
-          <t>Shopping Cart popup  window appears.</t>
-        </is>
-      </c>
-      <c r="J9" s="80" t="b">
+      <c r="K8" s="64"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="64"/>
+      <c r="P8" s="64"/>
+      <c r="Q8" s="64"/>
+    </row>
+    <row r="9" spans="1:17" s="74" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="64"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="64">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D9" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="64" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K9" s="70" t="n"/>
-      <c r="L9" s="70" t="n"/>
-      <c r="M9" s="70" t="n"/>
-      <c r="N9" s="70" t="n"/>
-      <c r="O9" s="70" t="n"/>
-      <c r="P9" s="70" t="n"/>
-      <c r="Q9" s="70" t="n"/>
-    </row>
-    <row r="10" ht="57" customFormat="1" customHeight="1" s="81">
-      <c r="A10" s="70" t="n"/>
-      <c r="B10" s="70" t="n"/>
-      <c r="C10" s="70">
-        <f>ROW(A10)-3</f>
-        <v/>
-      </c>
-      <c r="D10" s="70" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="E10" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F10" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Review the details on the shopping pop-up cart displayed at top right of screen.
-</t>
-        </is>
-      </c>
-      <c r="G10" s="70" t="n"/>
-      <c r="H10" s="89" t="inlineStr">
-        <is>
-          <t>
-</t>
-        </is>
-      </c>
-      <c r="I10" s="70" t="inlineStr">
-        <is>
-          <t>Details are reviewed.</t>
-        </is>
-      </c>
-      <c r="J10" s="80" t="b">
+      <c r="K9" s="64"/>
+      <c r="L9" s="64"/>
+      <c r="M9" s="64"/>
+      <c r="N9" s="64"/>
+      <c r="O9" s="64"/>
+      <c r="P9" s="64"/>
+      <c r="Q9" s="64"/>
+    </row>
+    <row r="10" spans="1:17" s="74" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="64"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="64">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="D10" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="64"/>
+      <c r="H10" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="64" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K10" s="70" t="n"/>
-      <c r="L10" s="70" t="n"/>
-      <c r="M10" s="70" t="n"/>
-      <c r="N10" s="70" t="n"/>
-      <c r="O10" s="70" t="n"/>
-      <c r="P10" s="70" t="n"/>
-      <c r="Q10" s="70" t="n"/>
-    </row>
-    <row r="11" ht="37.5" customFormat="1" customHeight="1" s="81">
-      <c r="A11" s="70" t="n"/>
-      <c r="B11" s="70" t="n"/>
-      <c r="C11" s="70">
-        <f>ROW(A11)-3</f>
-        <v/>
-      </c>
-      <c r="D11" s="70" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="E11" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F11" s="70" t="inlineStr">
-        <is>
-          <t>Checkout items in the cart by pressing "Check Out".
-Record the PR reference number as a result in Column K - Actual Result.</t>
-        </is>
-      </c>
-      <c r="G11" s="70" t="n"/>
-      <c r="H11" s="70" t="n"/>
-      <c r="I11" s="82" t="inlineStr">
-        <is>
-          <t>Requisition screen appears. The system assigns the PR number to the document.</t>
-        </is>
-      </c>
-      <c r="J11" s="80" t="b">
+      <c r="K10" s="64"/>
+      <c r="L10" s="64"/>
+      <c r="M10" s="64"/>
+      <c r="N10" s="64"/>
+      <c r="O10" s="64"/>
+      <c r="P10" s="64"/>
+      <c r="Q10" s="64"/>
+    </row>
+    <row r="11" spans="1:17" s="74" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="64"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="D11" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="64" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="75" t="s">
+        <v>63</v>
+      </c>
+      <c r="J11" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K11" s="79" t="n"/>
-      <c r="L11" s="70" t="n"/>
-      <c r="M11" s="70" t="n"/>
-      <c r="N11" s="70" t="n"/>
-      <c r="O11" s="70" t="n"/>
-      <c r="P11" s="70" t="n"/>
-      <c r="Q11" s="70" t="n"/>
-    </row>
-    <row r="12" ht="37.5" customFormat="1" customHeight="1" s="81">
-      <c r="A12" s="70" t="n"/>
-      <c r="B12" s="70" t="n"/>
-      <c r="C12" s="70">
-        <f>ROW(A12)-3</f>
-        <v/>
-      </c>
-      <c r="D12" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Header</t>
-        </is>
-      </c>
-      <c r="E12" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F12" s="83" t="inlineStr">
-        <is>
-          <t>_enter_ the requistion title on "Requistion title" box.</t>
-        </is>
-      </c>
-      <c r="G12" s="70" t="n"/>
-      <c r="H12" s="78" t="inlineStr">
-        <is>
-          <t>Safety Goggles Test PR</t>
-        </is>
-      </c>
-      <c r="I12" s="70" t="inlineStr">
-        <is>
-          <t>Requisition title is updated.</t>
-        </is>
-      </c>
-      <c r="J12" s="80" t="b">
+      <c r="K11" s="72"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="64"/>
+      <c r="O11" s="64"/>
+      <c r="P11" s="64"/>
+      <c r="Q11" s="64"/>
+    </row>
+    <row r="12" spans="1:17" s="74" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="64"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="64">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="D12" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="76" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="64"/>
+      <c r="H12" s="71" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="J12" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K12" s="70" t="n"/>
-      <c r="L12" s="70" t="n"/>
-      <c r="M12" s="70" t="n"/>
-      <c r="N12" s="70" t="n"/>
-      <c r="O12" s="70" t="n"/>
-      <c r="P12" s="70" t="n"/>
-      <c r="Q12" s="70" t="n"/>
-    </row>
-    <row r="13" ht="113.25" customFormat="1" customHeight="1" s="81">
-      <c r="A13" s="70" t="n"/>
-      <c r="B13" s="70" t="n"/>
-      <c r="C13" s="70">
-        <f>ROW(A13)-3</f>
-        <v/>
-      </c>
-      <c r="D13" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Header</t>
-        </is>
-      </c>
-      <c r="E13" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F13" s="82" t="inlineStr">
-        <is>
-          <t>_enter_ or verify the remaining data elements on the Requistion screen.
-Note: Only "red " items should be editable.</t>
-        </is>
-      </c>
-      <c r="G13" s="70" t="n"/>
-      <c r="H13" s="70" t="inlineStr">
-        <is>
-          <t>Need-by Date: Today + 7 days
-Deliver To: [Your Name ]
-Purchasing Unit:	[Leave default]
-On Behalf Of: [Your Name ]
-Plant: [Leave default]
-Company Code: [Leave default]</t>
-        </is>
-      </c>
-      <c r="I13" s="70" t="inlineStr">
-        <is>
-          <t>Fields are updated without any error.</t>
-        </is>
-      </c>
-      <c r="J13" s="80" t="b">
+      <c r="K12" s="64"/>
+      <c r="L12" s="64"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="64"/>
+      <c r="P12" s="64"/>
+      <c r="Q12" s="64"/>
+    </row>
+    <row r="13" spans="1:17" s="74" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="64"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="D13" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="75" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="64" t="s">
+        <v>70</v>
+      </c>
+      <c r="J13" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K13" s="70" t="n"/>
-      <c r="L13" s="70" t="n"/>
-      <c r="M13" s="70" t="n"/>
-      <c r="N13" s="70" t="n"/>
-      <c r="O13" s="70" t="n"/>
-      <c r="P13" s="70" t="n"/>
-      <c r="Q13" s="70" t="n"/>
-    </row>
-    <row r="14" ht="113.25" customFormat="1" customHeight="1" s="81">
-      <c r="A14" s="70" t="n"/>
-      <c r="B14" s="70" t="n"/>
-      <c r="C14" s="70">
-        <f>ROW(A14)-3</f>
-        <v/>
-      </c>
-      <c r="D14" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Lines</t>
-        </is>
-      </c>
-      <c r="E14" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F14" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_enter_ or  verify the information under the header area of item 1: 
-(Click on &gt; button on left of item image to expand the section )                             Note: Only "red " items should be editable.
-</t>
-        </is>
-      </c>
-      <c r="G14" s="70" t="n"/>
-      <c r="H14" s="84" t="inlineStr">
-        <is>
-          <t>Safety Goggles - Pro-Safe - Direct Ventilation
-Quantity : 1
-Net Amount: $3.49 USD
-Gross Amount: $3.49 USD
-Contact : Ariba Network Account</t>
-        </is>
-      </c>
-      <c r="I14" s="70" t="inlineStr">
-        <is>
-          <t>Fields are updated</t>
-        </is>
-      </c>
-      <c r="J14" s="80" t="b">
+      <c r="K13" s="64"/>
+      <c r="L13" s="64"/>
+      <c r="M13" s="64"/>
+      <c r="N13" s="64"/>
+      <c r="O13" s="64"/>
+      <c r="P13" s="64"/>
+      <c r="Q13" s="64"/>
+    </row>
+    <row r="14" spans="1:17" s="74" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="64"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="D14" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="64" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" s="64"/>
+      <c r="H14" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="I14" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K14" s="70" t="n"/>
-      <c r="L14" s="70" t="n"/>
-      <c r="M14" s="70" t="n"/>
-      <c r="N14" s="70" t="n"/>
-      <c r="O14" s="70" t="n"/>
-      <c r="P14" s="70" t="n"/>
-      <c r="Q14" s="70" t="n"/>
-    </row>
-    <row r="15" ht="113.25" customFormat="1" customHeight="1" s="81">
-      <c r="A15" s="70" t="n"/>
-      <c r="B15" s="70" t="n"/>
-      <c r="C15" s="70">
-        <f>ROW(A15)-3</f>
-        <v/>
-      </c>
-      <c r="D15" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Lines</t>
-        </is>
-      </c>
-      <c r="E15" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F15" s="83" t="inlineStr">
-        <is>
-          <t>Click on &gt; button on left of "Accounting" to expand the section.
-_enter_ or  verify the information in the Accounting  section. 
-Note: only red items should be editable.</t>
-        </is>
-      </c>
-      <c r="G15" s="70" t="n"/>
-      <c r="H15" s="70" t="inlineStr">
-        <is>
-          <t>Account Type: K (Cost Center)
-Item Category : Standard
-Bill To: 3020 (Texas Water Utilities, L.P.)
-Account Assignment : K (Cost center)
-GL Account:  Use default
-Cost Center: Use default</t>
-        </is>
-      </c>
-      <c r="I15" s="70" t="inlineStr">
-        <is>
-          <t>Fields are updated</t>
-        </is>
-      </c>
-      <c r="J15" s="80" t="b">
+      <c r="K14" s="64"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="64"/>
+      <c r="N14" s="64"/>
+      <c r="O14" s="64"/>
+      <c r="P14" s="64"/>
+      <c r="Q14" s="64"/>
+    </row>
+    <row r="15" spans="1:17" s="74" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="64"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="64">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="D15" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="76" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="64"/>
+      <c r="H15" s="64" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K15" s="70" t="n"/>
-      <c r="L15" s="70" t="n"/>
-      <c r="M15" s="70" t="n"/>
-      <c r="N15" s="70" t="n"/>
-      <c r="O15" s="70" t="n"/>
-      <c r="P15" s="70" t="n"/>
-      <c r="Q15" s="70" t="n"/>
-    </row>
-    <row r="16" ht="113.25" customFormat="1" customHeight="1" s="81">
-      <c r="A16" s="70" t="n"/>
-      <c r="B16" s="70" t="n"/>
-      <c r="C16" s="70">
-        <f>ROW(A16)-3</f>
-        <v/>
-      </c>
-      <c r="D16" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Lines</t>
-        </is>
-      </c>
-      <c r="E16" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F16" s="70" t="inlineStr">
-        <is>
-          <t>Click on &gt; button on left of "Shipping" to expand the section.
-_enter_ or  verify the information in the Shipping  section. 
-Note: only red items should be editable.</t>
-        </is>
-      </c>
-      <c r="G16" s="70" t="n"/>
-      <c r="H16" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Delivery Address: Use default
-Deliver To: [Your Name ]
-Need-by Date: Today +7
-Purchase Group: Use default
-</t>
-        </is>
-      </c>
-      <c r="I16" s="70" t="inlineStr">
-        <is>
-          <t>Fields are updated</t>
-        </is>
-      </c>
-      <c r="J16" s="80" t="b">
+      <c r="K15" s="64"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="64"/>
+      <c r="O15" s="64"/>
+      <c r="P15" s="64"/>
+      <c r="Q15" s="64"/>
+    </row>
+    <row r="16" spans="1:17" s="74" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="64"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="64">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="D16" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="64" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="64"/>
+      <c r="H16" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="I16" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="J16" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K16" s="70" t="n"/>
-      <c r="L16" s="70" t="n"/>
-      <c r="M16" s="70" t="n"/>
-      <c r="N16" s="70" t="n"/>
-      <c r="O16" s="70" t="n"/>
-      <c r="P16" s="70" t="n"/>
-      <c r="Q16" s="70" t="n"/>
-    </row>
-    <row r="17" ht="151.5" customFormat="1" customHeight="1" s="81">
-      <c r="A17" s="70" t="n"/>
-      <c r="B17" s="70" t="n"/>
-      <c r="C17" s="70">
-        <f>ROW(A17)-3</f>
-        <v/>
-      </c>
-      <c r="D17" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Lines</t>
-        </is>
-      </c>
-      <c r="E17" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F17" s="83" t="inlineStr">
-        <is>
-          <t>Click on &gt; button on left of "Others" to expand this section.
-_enter_ or  verify the information in the Others section. 
-Note: only red items should be editable.</t>
-        </is>
-      </c>
-      <c r="G17" s="70" t="n"/>
-      <c r="H17" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Commodity Code : 441115 (Organizers and accessories)
-Material Group : YBZ02 (Product Group Supplies)
-Item Category : Material
-Payment Terms :  Use default
-SAPPlant :  Use default
-Purch Org :  Use default
-Line item Text : [IGNORE]
-</t>
-        </is>
-      </c>
-      <c r="I17" s="70" t="inlineStr">
-        <is>
-          <t>Fields are updated.</t>
-        </is>
-      </c>
-      <c r="J17" s="80" t="b">
+      <c r="K16" s="64"/>
+      <c r="L16" s="64"/>
+      <c r="M16" s="64"/>
+      <c r="N16" s="64"/>
+      <c r="O16" s="64"/>
+      <c r="P16" s="64"/>
+      <c r="Q16" s="64"/>
+    </row>
+    <row r="17" spans="1:17" s="74" customFormat="1" ht="151.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="64"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="64">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="D17" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="76" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17" s="64"/>
+      <c r="H17" s="64" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="J17" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K17" s="70" t="n"/>
-      <c r="L17" s="70" t="n"/>
-      <c r="M17" s="70" t="n"/>
-      <c r="N17" s="70" t="n"/>
-      <c r="O17" s="70" t="n"/>
-      <c r="P17" s="70" t="n"/>
-      <c r="Q17" s="70" t="n"/>
-    </row>
-    <row r="18" ht="132" customFormat="1" customHeight="1" s="81">
-      <c r="A18" s="70" t="n"/>
-      <c r="B18" s="70" t="n"/>
-      <c r="C18" s="70">
-        <f>ROW(A18)-3</f>
-        <v/>
-      </c>
-      <c r="D18" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Header Comments</t>
-        </is>
-      </c>
-      <c r="E18" s="79" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F18" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Access the comments section. 
-_enter_ the information in the "Write your Comments"  section.                            
-Using the chooser, determine or verify if the comment should be visible to the supplier. 
-Note : only red items should be editable. </t>
-        </is>
-      </c>
-      <c r="G18" s="70" t="n"/>
-      <c r="H18" s="70" t="inlineStr">
-        <is>
-          <t>Comments: [Blank]
-Share with Supplier: [Not Checked]</t>
-        </is>
-      </c>
-      <c r="I18" s="70" t="inlineStr">
-        <is>
-          <t>You are able to write the comments with the desired visibility of the supplier.</t>
-        </is>
-      </c>
-      <c r="J18" s="80" t="b">
+      <c r="K17" s="64"/>
+      <c r="L17" s="64"/>
+      <c r="M17" s="64"/>
+      <c r="N17" s="64"/>
+      <c r="O17" s="64"/>
+      <c r="P17" s="64"/>
+      <c r="Q17" s="64"/>
+    </row>
+    <row r="18" spans="1:17" s="74" customFormat="1" ht="132" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="64"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="64">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="D18" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="72" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="64"/>
+      <c r="H18" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="I18" s="64" t="s">
+        <v>85</v>
+      </c>
+      <c r="J18" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K18" s="70" t="n"/>
-      <c r="L18" s="70" t="n"/>
-      <c r="M18" s="70" t="n"/>
-      <c r="N18" s="70" t="n"/>
-      <c r="O18" s="70" t="n"/>
-      <c r="P18" s="70" t="n"/>
-      <c r="Q18" s="70" t="n"/>
-    </row>
-    <row r="19" ht="75.75" customFormat="1" customHeight="1" s="81">
-      <c r="A19" s="70" t="n"/>
-      <c r="B19" s="70" t="n"/>
-      <c r="C19" s="70">
-        <f>ROW(A19)-3</f>
-        <v/>
-      </c>
-      <c r="D19" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Header Comments</t>
-        </is>
-      </c>
-      <c r="E19" s="79" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F19" s="70" t="inlineStr">
-        <is>
-          <t>Press "Add"  to save Comments updates.</t>
-        </is>
-      </c>
-      <c r="G19" s="70" t="n"/>
-      <c r="H19" s="70" t="n"/>
-      <c r="I19" s="70" t="inlineStr">
-        <is>
-          <t>Added Comments page is displayed. Comments section displays Creator, Comment, Shared with supplier info and date created.</t>
-        </is>
-      </c>
-      <c r="J19" s="80" t="b">
+      <c r="K18" s="64"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="64"/>
+      <c r="O18" s="64"/>
+      <c r="P18" s="64"/>
+      <c r="Q18" s="64"/>
+    </row>
+    <row r="19" spans="1:17" s="74" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="64"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="64">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="D19" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="72" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="64" t="s">
+        <v>86</v>
+      </c>
+      <c r="G19" s="64"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="J19" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K19" s="70" t="n"/>
-      <c r="L19" s="70" t="n"/>
-      <c r="M19" s="70" t="n"/>
-      <c r="N19" s="70" t="n"/>
-      <c r="O19" s="70" t="n"/>
-      <c r="P19" s="70" t="n"/>
-      <c r="Q19" s="70" t="n"/>
-    </row>
-    <row r="20" ht="57" customFormat="1" customHeight="1" s="81">
-      <c r="A20" s="70" t="n"/>
-      <c r="B20" s="70" t="n"/>
-      <c r="C20" s="70">
-        <f>ROW(A20)-3</f>
-        <v/>
-      </c>
-      <c r="D20" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Header Attachments</t>
-        </is>
-      </c>
-      <c r="E20" s="79" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F20" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Access "Attachments" section. 
-Press "Browse" to add an attachment.
-</t>
-        </is>
-      </c>
-      <c r="G20" s="70" t="n"/>
-      <c r="H20" s="70" t="n"/>
-      <c r="I20" s="70" t="inlineStr">
-        <is>
-          <t>File system window appears</t>
-        </is>
-      </c>
-      <c r="J20" s="80" t="b">
+      <c r="K19" s="64"/>
+      <c r="L19" s="64"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="64"/>
+      <c r="O19" s="64"/>
+      <c r="P19" s="64"/>
+      <c r="Q19" s="64"/>
+    </row>
+    <row r="20" spans="1:17" s="74" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="64"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="64">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="D20" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" s="72" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="64" t="s">
+        <v>89</v>
+      </c>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="64" t="s">
+        <v>90</v>
+      </c>
+      <c r="J20" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K20" s="70" t="n"/>
-      <c r="L20" s="70" t="n"/>
-      <c r="M20" s="70" t="n"/>
-      <c r="N20" s="70" t="n"/>
-      <c r="O20" s="70" t="n"/>
-      <c r="P20" s="70" t="n"/>
-      <c r="Q20" s="70" t="n"/>
-    </row>
-    <row r="21" ht="57" customFormat="1" customHeight="1" s="81">
-      <c r="A21" s="70" t="n"/>
-      <c r="B21" s="70" t="n"/>
-      <c r="C21" s="70">
-        <f>ROW(A21)-3</f>
-        <v/>
-      </c>
-      <c r="D21" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Header Attachments</t>
-        </is>
-      </c>
-      <c r="E21" s="79" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F21" s="70" t="inlineStr">
-        <is>
-          <t>Select the desired file to be attached, and press "Open".</t>
-        </is>
-      </c>
-      <c r="G21" s="70" t="n"/>
-      <c r="H21" s="70" t="n"/>
-      <c r="I21" s="70" t="inlineStr">
-        <is>
-          <t>File is uploaded to Ariba Buying. File name is displayed.</t>
-        </is>
-      </c>
-      <c r="J21" s="80" t="b">
+      <c r="K20" s="64"/>
+      <c r="L20" s="64"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="64"/>
+      <c r="O20" s="64"/>
+      <c r="P20" s="64"/>
+      <c r="Q20" s="64"/>
+    </row>
+    <row r="21" spans="1:17" s="74" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="64"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="64">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="D21" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="72" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="J21" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K21" s="70" t="n"/>
-      <c r="L21" s="70" t="n"/>
-      <c r="M21" s="70" t="n"/>
-      <c r="N21" s="70" t="n"/>
-      <c r="O21" s="70" t="n"/>
-      <c r="P21" s="70" t="n"/>
-      <c r="Q21" s="70" t="n"/>
-    </row>
-    <row r="22" ht="57" customFormat="1" customHeight="1" s="81">
-      <c r="A22" s="70" t="n"/>
-      <c r="B22" s="70" t="n"/>
-      <c r="C22" s="70">
-        <f>ROW(A22)-3</f>
-        <v/>
-      </c>
-      <c r="D22" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Header Attachments</t>
-        </is>
-      </c>
-      <c r="E22" s="79" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F22" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Using the checkbox , determine or verify if the attachement should be visible to the supplier. </t>
-        </is>
-      </c>
-      <c r="G22" s="70" t="n"/>
-      <c r="H22" s="70" t="inlineStr">
-        <is>
-          <t>Share with Supplier: [Not selected]</t>
-        </is>
-      </c>
-      <c r="I22" s="70" t="n"/>
-      <c r="J22" s="80" t="b">
+      <c r="K21" s="64"/>
+      <c r="L21" s="64"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="64"/>
+      <c r="O21" s="64"/>
+      <c r="P21" s="64"/>
+      <c r="Q21" s="64"/>
+    </row>
+    <row r="22" spans="1:17" s="74" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="64"/>
+      <c r="B22" s="64"/>
+      <c r="C22" s="64">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="D22" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="72" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="64" t="s">
+        <v>93</v>
+      </c>
+      <c r="G22" s="64"/>
+      <c r="H22" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="I22" s="64"/>
+      <c r="J22" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K22" s="70" t="n"/>
-      <c r="L22" s="70" t="n"/>
-      <c r="M22" s="70" t="n"/>
-      <c r="N22" s="70" t="n"/>
-      <c r="O22" s="70" t="n"/>
-      <c r="P22" s="70" t="n"/>
-      <c r="Q22" s="70" t="n"/>
-    </row>
-    <row r="23" ht="57" customFormat="1" customHeight="1" s="81">
-      <c r="A23" s="70" t="n"/>
-      <c r="B23" s="70" t="n"/>
-      <c r="C23" s="70">
-        <f>ROW(A23)-3</f>
-        <v/>
-      </c>
-      <c r="D23" s="70" t="inlineStr">
-        <is>
-          <t>Requisition Header Attachments</t>
-        </is>
-      </c>
-      <c r="E23" s="79" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F23" s="70" t="inlineStr">
-        <is>
-          <t>Press "Add"  to save Attachment.</t>
-        </is>
-      </c>
-      <c r="G23" s="70" t="n"/>
-      <c r="H23" s="70" t="n"/>
-      <c r="I23" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Attachment file name, size, Creator, and visible to supplier on Order is visible.</t>
-        </is>
-      </c>
-      <c r="J23" s="80" t="b">
+      <c r="K22" s="64"/>
+      <c r="L22" s="64"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="64"/>
+      <c r="O22" s="64"/>
+      <c r="P22" s="64"/>
+      <c r="Q22" s="64"/>
+    </row>
+    <row r="23" spans="1:17" s="74" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="64"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="64">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="D23" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" s="72" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="G23" s="64"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="J23" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K23" s="70" t="n"/>
-      <c r="L23" s="70" t="n"/>
-      <c r="M23" s="70" t="n"/>
-      <c r="N23" s="70" t="n"/>
-      <c r="O23" s="70" t="n"/>
-      <c r="P23" s="70" t="n"/>
-      <c r="Q23" s="70" t="n"/>
-    </row>
-    <row r="24" ht="37.5" customFormat="1" customHeight="1" s="81">
-      <c r="A24" s="70" t="n"/>
-      <c r="B24" s="70" t="n"/>
-      <c r="C24" s="70">
-        <f>ROW(A24)-3</f>
-        <v/>
-      </c>
-      <c r="D24" s="70" t="inlineStr">
-        <is>
-          <t>Approval Flow</t>
-        </is>
-      </c>
-      <c r="E24" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F24" s="85" t="inlineStr">
-        <is>
-          <t>Verify the approval flow displayed under Approval Flow header at bottom of the screen.</t>
-        </is>
-      </c>
-      <c r="G24" s="86" t="n"/>
-      <c r="H24" s="86" t="inlineStr">
-        <is>
-          <t>Approver/s are shown.</t>
-        </is>
-      </c>
-      <c r="I24" s="86" t="inlineStr">
-        <is>
-          <t>Respective approvers are displayed.</t>
-        </is>
-      </c>
-      <c r="J24" s="80" t="b">
+      <c r="K23" s="64"/>
+      <c r="L23" s="64"/>
+      <c r="M23" s="64"/>
+      <c r="N23" s="64"/>
+      <c r="O23" s="64"/>
+      <c r="P23" s="64"/>
+      <c r="Q23" s="64"/>
+    </row>
+    <row r="24" spans="1:17" s="74" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="64"/>
+      <c r="B24" s="64"/>
+      <c r="C24" s="64">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D24" s="64" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="78" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" s="79"/>
+      <c r="H24" s="79" t="s">
+        <v>99</v>
+      </c>
+      <c r="I24" s="79" t="s">
+        <v>100</v>
+      </c>
+      <c r="J24" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K24" s="70" t="n"/>
-      <c r="L24" s="70" t="n"/>
-      <c r="M24" s="70" t="n"/>
-      <c r="N24" s="70" t="n"/>
-      <c r="O24" s="70" t="n"/>
-      <c r="P24" s="70" t="n"/>
-      <c r="Q24" s="70" t="n"/>
-    </row>
-    <row r="25" ht="37.5" customFormat="1" customHeight="1" s="81">
-      <c r="A25" s="70" t="n"/>
-      <c r="B25" s="70" t="n"/>
-      <c r="C25" s="70">
-        <f>ROW(A25)-3</f>
-        <v/>
-      </c>
-      <c r="D25" s="70" t="inlineStr">
-        <is>
-          <t>Requisition</t>
-        </is>
-      </c>
-      <c r="E25" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F25" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Press "Submit"  to submit the requisition for approval. </t>
-        </is>
-      </c>
-      <c r="G25" s="86" t="n"/>
-      <c r="H25" s="86" t="n"/>
-      <c r="I25" s="86" t="inlineStr">
-        <is>
-          <t>Message appears "Your requisition has been sent for approval.</t>
-        </is>
-      </c>
-      <c r="J25" s="80" t="b">
+      <c r="K24" s="64"/>
+      <c r="L24" s="64"/>
+      <c r="M24" s="64"/>
+      <c r="N24" s="64"/>
+      <c r="O24" s="64"/>
+      <c r="P24" s="64"/>
+      <c r="Q24" s="64"/>
+    </row>
+    <row r="25" spans="1:17" s="74" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="64"/>
+      <c r="B25" s="64"/>
+      <c r="C25" s="64">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D25" s="64" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="78" t="s">
+        <v>102</v>
+      </c>
+      <c r="G25" s="79"/>
+      <c r="H25" s="79"/>
+      <c r="I25" s="79" t="s">
+        <v>103</v>
+      </c>
+      <c r="J25" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K25" s="70" t="n"/>
-      <c r="L25" s="70" t="n"/>
-      <c r="M25" s="70" t="n"/>
-      <c r="N25" s="70" t="n"/>
-      <c r="O25" s="70" t="n"/>
-      <c r="P25" s="70" t="n"/>
-      <c r="Q25" s="70" t="n"/>
-    </row>
-    <row r="26" ht="57" customFormat="1" customHeight="1" s="81">
-      <c r="A26" s="70" t="n"/>
-      <c r="B26" s="70" t="n"/>
-      <c r="C26" s="70">
-        <f>ROW(A26)-3</f>
-        <v/>
-      </c>
-      <c r="D26" s="70" t="inlineStr">
-        <is>
-          <t>View Approval Flow</t>
-        </is>
-      </c>
-      <c r="E26" s="70" t="inlineStr">
-        <is>
-          <t>Buyer</t>
-        </is>
-      </c>
-      <c r="F26" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Click on View Requisition to display the created requisiton. </t>
-        </is>
-      </c>
-      <c r="G26" s="86" t="n"/>
-      <c r="H26" s="86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-Submitted</t>
-        </is>
-      </c>
-      <c r="I26" s="82" t="inlineStr">
-        <is>
-          <t>The PR is now on Submitted status.
-Approval Flow is now active shown by green flow.</t>
-        </is>
-      </c>
-      <c r="J26" s="80" t="b">
+      <c r="K25" s="64"/>
+      <c r="L25" s="64"/>
+      <c r="M25" s="64"/>
+      <c r="N25" s="64"/>
+      <c r="O25" s="64"/>
+      <c r="P25" s="64"/>
+      <c r="Q25" s="64"/>
+    </row>
+    <row r="26" spans="1:17" s="74" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="64"/>
+      <c r="B26" s="64"/>
+      <c r="C26" s="64">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D26" s="64" t="s">
+        <v>104</v>
+      </c>
+      <c r="E26" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="G26" s="79"/>
+      <c r="H26" s="79" t="s">
+        <v>106</v>
+      </c>
+      <c r="I26" s="75" t="s">
+        <v>107</v>
+      </c>
+      <c r="J26" s="73" t="b">
         <v>0</v>
       </c>
-      <c r="K26" s="70" t="n"/>
-      <c r="L26" s="70" t="n"/>
-      <c r="M26" s="70" t="n"/>
-      <c r="N26" s="70" t="n"/>
-      <c r="O26" s="70" t="n"/>
-      <c r="P26" s="70" t="n"/>
-      <c r="Q26" s="70" t="n"/>
+      <c r="K26" s="64"/>
+      <c r="L26" s="64"/>
+      <c r="M26" s="64"/>
+      <c r="N26" s="64"/>
+      <c r="O26" s="64"/>
+      <c r="P26" s="64"/>
+      <c r="Q26" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="Q1:Q2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="H1:H2"/>
@@ -6412,387 +6395,295 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="Q1:Q2"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="O4:O26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O4:O26">
       <formula1>"10 - Not Started,20 - In-Process,30 - TPR Hold,40 - DEV Hold,50 - Pass,60 - N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="L4:L26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:L26">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E26">
       <formula1>"AP,Buyer,PO Approv,Inv Approv,Watcher,SAP Tech Team,Prem Tech,Prem Funct"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.45" right="0.45" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" scale="61" fitToHeight="10" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup scale="61" fitToHeight="10" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R46"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="17.25" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="14.85546875" customWidth="1" style="2" min="1" max="1"/>
-    <col width="8.42578125" customWidth="1" style="2" min="2" max="2"/>
-    <col width="14.28515625" customWidth="1" style="2" min="3" max="7"/>
-    <col width="14.28515625" customWidth="1" style="1" min="8" max="9"/>
-    <col width="11.7109375" customWidth="1" style="1" min="10" max="11"/>
-    <col width="14.28515625" bestFit="1" customWidth="1" style="1" min="12" max="17"/>
-    <col width="11.7109375" bestFit="1" customWidth="1" style="1" min="18" max="18"/>
-    <col width="9.140625" customWidth="1" style="1" min="19" max="16384"/>
+    <col min="1" max="1" width="14.88671875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" style="2" customWidth="1"/>
+    <col min="3" max="7" width="14.33203125" style="2" customWidth="1"/>
+    <col min="8" max="9" width="14.33203125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="11.6640625" style="1" customWidth="1"/>
+    <col min="12" max="17" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.109375" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="17.25" customHeight="1" thickBot="1"/>
-    <row r="3" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>Count of Status</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="20" t="n"/>
-      <c r="G3" s="20" t="n"/>
-      <c r="H3" s="20" t="n"/>
-      <c r="I3" s="20" t="n"/>
-      <c r="J3" s="21" t="n"/>
-    </row>
-    <row r="4" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>__changed Number</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>(blank)</t>
-        </is>
-      </c>
-      <c r="D4" s="22" t="inlineStr">
-        <is>
-          <t>10 - Not Started</t>
-        </is>
-      </c>
-      <c r="E4" s="22" t="inlineStr">
-        <is>
-          <t>20 - In-Process</t>
-        </is>
-      </c>
-      <c r="F4" s="22" t="inlineStr">
-        <is>
-          <t>30 - TPR Hold</t>
-        </is>
-      </c>
-      <c r="G4" s="22" t="inlineStr">
-        <is>
-          <t>40 - DEV Hold</t>
-        </is>
-      </c>
-      <c r="H4" s="22" t="inlineStr">
-        <is>
-          <t>50 - Pass</t>
-        </is>
-      </c>
-      <c r="I4" s="33" t="inlineStr">
-        <is>
-          <t>60 - N/A</t>
-        </is>
-      </c>
-      <c r="J4" s="23" t="inlineStr">
-        <is>
-          <t>Grand Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="12.75" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>PP_018</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>RTR</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="4" t="n">
+    <row r="1" spans="1:10" ht="11.4" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="21"/>
+    </row>
+    <row r="4" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="6" t="n">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="26" t="n"/>
-      <c r="B6" s="25" t="inlineStr">
-        <is>
-          <t>PTP</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="27" t="n">
+    <row r="6" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="26"/>
+      <c r="B6" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="27">
         <v>1</v>
       </c>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="27" t="n"/>
-      <c r="H6" s="27" t="n">
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27">
         <v>8</v>
       </c>
-      <c r="I6" s="27" t="n">
+      <c r="I6" s="27">
         <v>2</v>
       </c>
-      <c r="J6" s="28" t="n">
+      <c r="J6" s="28">
         <v>11</v>
       </c>
     </row>
-    <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="26" t="n"/>
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-      <c r="C7" s="24" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n">
+    <row r="7" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="26"/>
+      <c r="B7" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27">
         <v>25</v>
       </c>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="28" t="n">
+      <c r="I7" s="27"/>
+      <c r="J7" s="28">
         <v>25</v>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A8" s="29" t="n"/>
-      <c r="B8" s="30" t="inlineStr">
-        <is>
-          <t>IMWM</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="27" t="n"/>
-      <c r="H8" s="27" t="n">
+    <row r="8" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="29"/>
+      <c r="B8" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="24"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27">
         <v>5</v>
       </c>
-      <c r="I8" s="27" t="n">
+      <c r="I8" s="27">
         <v>4</v>
       </c>
-      <c r="J8" s="28" t="n">
+      <c r="J8" s="28">
         <v>9</v>
       </c>
     </row>
-    <row r="9" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>PP_018 Total</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="10" t="n">
+    <row r="9" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10">
         <v>2</v>
       </c>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="10" t="n"/>
-      <c r="G9" s="10" t="n"/>
-      <c r="H9" s="10" t="n">
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10">
         <v>38</v>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="I9" s="10">
         <v>6</v>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="J9" s="11">
         <v>46</v>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>ZZZ999</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="10" t="n">
+    <row r="10" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10">
         <v>1</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="10">
         <v>1</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="10">
         <v>1</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="10">
         <v>1</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H10" s="10">
         <v>1</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="I10" s="10">
         <v>1</v>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="J10" s="11">
         <v>6</v>
       </c>
     </row>
-    <row r="11" ht="17.25" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>ZZZ999 Total</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="4" t="n">
+    <row r="11" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="31"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="4">
         <v>1</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="4">
         <v>1</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="4">
         <v>1</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="4">
         <v>1</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="4">
         <v>1</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="12" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Grand Total</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="10" t="n">
+    <row r="12" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="8"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10">
         <v>3</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="10">
         <v>1</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="10">
         <v>1</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="10">
         <v>1</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="H12" s="10">
         <v>39</v>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="I12" s="10">
         <v>7</v>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="J12" s="11">
         <v>52</v>
       </c>
     </row>
-    <row r="13" ht="17.25" customHeight="1"/>
-    <row r="14" ht="17.25" customHeight="1"/>
-    <row r="15" ht="17.25" customHeight="1"/>
-    <row r="16" ht="17.25" customHeight="1"/>
-    <row r="17" ht="17.25" customHeight="1"/>
-    <row r="18" ht="17.25" customHeight="1"/>
-    <row r="19" ht="17.25" customHeight="1"/>
-    <row r="20" ht="17.25" customHeight="1"/>
-    <row r="21" ht="17.25" customHeight="1"/>
-    <row r="22" ht="17.25" customHeight="1"/>
-    <row r="23" ht="17.25" customHeight="1"/>
-    <row r="24" ht="17.25" customHeight="1"/>
-    <row r="25" ht="17.25" customHeight="1"/>
-    <row r="26" ht="17.25" customHeight="1"/>
-    <row r="27" ht="17.25" customHeight="1"/>
-    <row r="28" ht="17.25" customHeight="1"/>
-    <row r="29" ht="17.25" customHeight="1"/>
-    <row r="30" ht="17.25" customHeight="1"/>
-    <row r="31" ht="17.25" customHeight="1"/>
-    <row r="32" ht="17.25" customHeight="1"/>
-    <row r="33" ht="17.25" customHeight="1"/>
-    <row r="34" ht="17.25" customHeight="1"/>
-    <row r="35" ht="17.25" customHeight="1"/>
-    <row r="36" ht="17.25" customHeight="1"/>
-    <row r="37" ht="17.25" customHeight="1"/>
-    <row r="38" ht="17.25" customHeight="1"/>
-    <row r="39" ht="17.25" customHeight="1"/>
-    <row r="40" ht="17.25" customHeight="1"/>
-    <row r="41" ht="17.25" customHeight="1"/>
-    <row r="42" ht="17.25" customHeight="1"/>
-    <row r="43" ht="17.25" customHeight="1"/>
-    <row r="44" ht="17.25" customHeight="1"/>
-    <row r="45" ht="17.25" customHeight="1"/>
-    <row r="46" ht="17.25" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
